--- a/partesa/vino/listavino.xlsx
+++ b/partesa/vino/listavino.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Dropbox\doc lavoro\2026\vino\lisino vino\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Dropbox\doc lavoro\2026\vino\lisino vino\vino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975F9B15-6111-4AAC-8438-9BED16C82F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5637FCE4-6C64-4E4C-B241-4FA308DEF2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5840" uniqueCount="2888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5840" uniqueCount="2887">
   <si>
     <t>Regione/Nazione</t>
   </si>
@@ -5751,9 +5751,6 @@
   </si>
   <si>
     <t xml:space="preserve">AUDARYA NURAGUS SPUMANTE BRUT </t>
-  </si>
-  <si>
-    <t>75 cl</t>
   </si>
   <si>
     <t>https://horecapp.it/sinc/genera-pdf-test.php?prodottiinpagine=F1047</t>
@@ -32233,7 +32230,7 @@
         <v>1909</v>
       </c>
       <c r="E744" s="14" t="s">
-        <v>1910</v>
+        <v>38</v>
       </c>
       <c r="F744" s="17">
         <v>6</v>
@@ -32245,7 +32242,7 @@
         <v>57</v>
       </c>
       <c r="I744" s="51" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="745" spans="1:9">
@@ -32253,13 +32250,13 @@
         <v>1907</v>
       </c>
       <c r="B745" s="5" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C745" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D745" s="6" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="E745" s="14" t="s">
         <v>38</v>
@@ -32274,7 +32271,7 @@
         <v>44.400000000000013</v>
       </c>
       <c r="I745" s="51" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="746" spans="1:9">
@@ -32282,13 +32279,13 @@
         <v>1907</v>
       </c>
       <c r="B746" s="5" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="C746" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D746" s="6" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="E746" s="14" t="s">
         <v>38</v>
@@ -32303,7 +32300,7 @@
         <v>48</v>
       </c>
       <c r="I746" s="51" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="747" spans="1:9">
@@ -32311,13 +32308,13 @@
         <v>1907</v>
       </c>
       <c r="B747" s="5" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="C747" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D747" s="6" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="E747" s="14" t="s">
         <v>38</v>
@@ -32332,7 +32329,7 @@
         <v>55.2</v>
       </c>
       <c r="I747" s="51" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="748" spans="1:9">
@@ -32340,13 +32337,13 @@
         <v>1907</v>
       </c>
       <c r="B748" s="5" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="C748" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D748" s="6" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="E748" s="14" t="s">
         <v>38</v>
@@ -32361,7 +32358,7 @@
         <v>75</v>
       </c>
       <c r="I748" s="51" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="749" spans="1:9">
@@ -32369,13 +32366,13 @@
         <v>1907</v>
       </c>
       <c r="B749" s="5" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="C749" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D749" s="6" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="E749" s="14" t="s">
         <v>38</v>
@@ -32390,7 +32387,7 @@
         <v>67.5</v>
       </c>
       <c r="I749" s="51" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="750" spans="1:9">
@@ -32398,13 +32395,13 @@
         <v>1907</v>
       </c>
       <c r="B750" s="5" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="C750" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D750" s="6" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E750" s="14" t="s">
         <v>38</v>
@@ -32419,7 +32416,7 @@
         <v>45.900000000000013</v>
       </c>
       <c r="I750" s="51" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="751" spans="1:9">
@@ -32427,13 +32424,13 @@
         <v>1907</v>
       </c>
       <c r="B751" s="5" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="C751" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D751" s="6" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="E751" s="14" t="s">
         <v>38</v>
@@ -32448,7 +32445,7 @@
         <v>45.900000000000013</v>
       </c>
       <c r="I751" s="51" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="752" spans="1:9">
@@ -32456,13 +32453,13 @@
         <v>1907</v>
       </c>
       <c r="B752" s="5" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="C752" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D752" s="6" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="E752" s="14" t="s">
         <v>38</v>
@@ -32477,7 +32474,7 @@
         <v>47.7</v>
       </c>
       <c r="I752" s="51" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="753" spans="1:9">
@@ -32485,13 +32482,13 @@
         <v>1907</v>
       </c>
       <c r="B753" s="5" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="C753" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D753" s="6" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="E753" s="14" t="s">
         <v>38</v>
@@ -32506,7 +32503,7 @@
         <v>104.7</v>
       </c>
       <c r="I753" s="51" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="754" spans="1:9">
@@ -32514,13 +32511,13 @@
         <v>1907</v>
       </c>
       <c r="B754" s="5" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="C754" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D754" s="6" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E754" s="14" t="s">
         <v>38</v>
@@ -32535,7 +32532,7 @@
         <v>168</v>
       </c>
       <c r="I754" s="51" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="755" spans="1:9">
@@ -32543,13 +32540,13 @@
         <v>1907</v>
       </c>
       <c r="B755" s="5" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="C755" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D755" s="6" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="E755" s="14" t="s">
         <v>941</v>
@@ -32564,7 +32561,7 @@
         <v>13.35</v>
       </c>
       <c r="I755" s="51" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="756" spans="1:9">
@@ -32586,13 +32583,13 @@
         <v>1907</v>
       </c>
       <c r="B757" s="5" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="C757" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D757" s="6" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="E757" s="14" t="s">
         <v>139</v>
@@ -32607,7 +32604,7 @@
         <v>57.600000000000009</v>
       </c>
       <c r="I757" s="51" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="758" spans="1:9">
@@ -32629,13 +32626,13 @@
         <v>1907</v>
       </c>
       <c r="B759" s="5" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="C759" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D759" s="6" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="E759" s="14" t="s">
         <v>65</v>
@@ -32650,7 +32647,7 @@
         <v>27</v>
       </c>
       <c r="I759" s="51" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="760" spans="1:9">
@@ -32658,13 +32655,13 @@
         <v>1907</v>
       </c>
       <c r="B760" s="5" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="C760" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D760" s="6" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="E760" s="14" t="s">
         <v>65</v>
@@ -32679,7 +32676,7 @@
         <v>42.5</v>
       </c>
       <c r="I760" s="51" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="761" spans="1:9">
@@ -32687,13 +32684,13 @@
         <v>1907</v>
       </c>
       <c r="B761" s="5" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="C761" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D761" s="6" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E761" s="14" t="s">
         <v>65</v>
@@ -32708,7 +32705,7 @@
         <v>65</v>
       </c>
       <c r="I761" s="51" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="762" spans="1:9">
@@ -32730,13 +32727,13 @@
         <v>1907</v>
       </c>
       <c r="B763" s="5" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="C763" s="23" t="s">
         <v>157</v>
       </c>
       <c r="D763" s="6" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="E763" s="14"/>
       <c r="F763" s="17">
@@ -32749,12 +32746,12 @@
         <v>34</v>
       </c>
       <c r="I763" s="51" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="764" spans="1:9">
       <c r="A764" s="2" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B764" s="24"/>
       <c r="C764" s="24"/>
@@ -32769,13 +32766,13 @@
         <v>1907</v>
       </c>
       <c r="B765" s="5" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C765" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D765" s="6" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="E765" s="14" t="s">
         <v>38</v>
@@ -32790,7 +32787,7 @@
         <v>49.5</v>
       </c>
       <c r="I765" s="51" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="766" spans="1:9">
@@ -32798,13 +32795,13 @@
         <v>1907</v>
       </c>
       <c r="B766" s="5" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="C766" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D766" s="6" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="E766" s="14" t="s">
         <v>38</v>
@@ -32819,7 +32816,7 @@
         <v>59.100000000000009</v>
       </c>
       <c r="I766" s="51" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="767" spans="1:9">
@@ -32827,13 +32824,13 @@
         <v>1907</v>
       </c>
       <c r="B767" s="5" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C767" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D767" s="6" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="E767" s="14" t="s">
         <v>38</v>
@@ -32848,7 +32845,7 @@
         <v>49.5</v>
       </c>
       <c r="I767" s="51" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="768" spans="1:9">
@@ -32856,13 +32853,13 @@
         <v>1907</v>
       </c>
       <c r="B768" s="5" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="C768" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D768" s="6" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="E768" s="14" t="s">
         <v>38</v>
@@ -32877,7 +32874,7 @@
         <v>59.100000000000009</v>
       </c>
       <c r="I768" s="51" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="769" spans="1:9" ht="15.6" customHeight="1">
@@ -32885,7 +32882,7 @@
       <c r="B769" s="45"/>
       <c r="C769" s="46"/>
       <c r="D769" s="47" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="E769" s="46"/>
       <c r="F769" s="46"/>
@@ -32894,7 +32891,7 @@
     </row>
     <row r="770" spans="1:9">
       <c r="A770" s="2" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B770" s="24"/>
       <c r="C770" s="24"/>
@@ -32906,16 +32903,16 @@
     </row>
     <row r="771" spans="1:9">
       <c r="A771" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B771" s="5" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="C771" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D771" s="6" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="E771" s="14" t="s">
         <v>38</v>
@@ -32930,21 +32927,21 @@
         <v>192</v>
       </c>
       <c r="I771" s="51" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="772" spans="1:9">
       <c r="A772" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B772" s="5" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C772" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D772" s="6" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="E772" s="14" t="s">
         <v>38</v>
@@ -32959,21 +32956,21 @@
         <v>234</v>
       </c>
       <c r="I772" s="51" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="773" spans="1:9">
       <c r="A773" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B773" s="5" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="C773" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D773" s="6" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E773" s="14" t="s">
         <v>38</v>
@@ -32988,21 +32985,21 @@
         <v>228</v>
       </c>
       <c r="I773" s="51" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="774" spans="1:9">
       <c r="A774" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B774" s="5" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="C774" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D774" s="6" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E774" s="14" t="s">
         <v>38</v>
@@ -33017,21 +33014,21 @@
         <v>95</v>
       </c>
       <c r="I774" s="51" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="775" spans="1:9">
       <c r="A775" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B775" s="5" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="C775" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D775" s="6" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="E775" s="14" t="s">
         <v>38</v>
@@ -33046,7 +33043,7 @@
         <v>29</v>
       </c>
       <c r="I775" s="51" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="776" spans="1:9">
@@ -33065,16 +33062,16 @@
     </row>
     <row r="777" spans="1:9">
       <c r="A777" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B777" s="5" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="C777" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D777" s="6" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="E777" s="14" t="s">
         <v>65</v>
@@ -33089,21 +33086,21 @@
         <v>69</v>
       </c>
       <c r="I777" s="51" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="778" spans="1:9">
       <c r="A778" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B778" s="5" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C778" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D778" s="6" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="E778" s="14" t="s">
         <v>65</v>
@@ -33118,21 +33115,21 @@
         <v>85</v>
       </c>
       <c r="I778" s="51" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="779" spans="1:9">
       <c r="A779" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B779" s="5" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="C779" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D779" s="6" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E779" s="14" t="s">
         <v>65</v>
@@ -33147,21 +33144,21 @@
         <v>80</v>
       </c>
       <c r="I779" s="51" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="780" spans="1:9">
       <c r="A780" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B780" s="5" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="C780" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D780" s="6" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E780" s="14" t="s">
         <v>65</v>
@@ -33176,21 +33173,21 @@
         <v>200</v>
       </c>
       <c r="I780" s="51" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="781" spans="1:9">
       <c r="A781" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B781" s="5" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="C781" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D781" s="6" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="E781" s="14" t="s">
         <v>65</v>
@@ -33205,12 +33202,12 @@
         <v>29</v>
       </c>
       <c r="I781" s="51" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="782" spans="1:9">
       <c r="A782" s="2" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B782" s="24"/>
       <c r="C782" s="24"/>
@@ -33222,16 +33219,16 @@
     </row>
     <row r="783" spans="1:9">
       <c r="A783" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B783" s="5" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="C783" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D783" s="6" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E783" s="14" t="s">
         <v>38</v>
@@ -33246,21 +33243,21 @@
         <v>186.3</v>
       </c>
       <c r="I783" s="51" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="784" spans="1:9">
       <c r="A784" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B784" s="5" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C784" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D784" s="6" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="E784" s="14" t="s">
         <v>38</v>
@@ -33275,21 +33272,21 @@
         <v>34.15</v>
       </c>
       <c r="I784" s="51" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="785" spans="1:9">
       <c r="A785" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B785" s="5" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C785" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D785" s="6" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E785" s="14" t="s">
         <v>38</v>
@@ -33304,21 +33301,21 @@
         <v>207.9</v>
       </c>
       <c r="I785" s="51" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="786" spans="1:9">
       <c r="A786" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B786" s="5" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C786" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D786" s="6" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E786" s="14" t="s">
         <v>38</v>
@@ -33333,21 +33330,21 @@
         <v>402.3</v>
       </c>
       <c r="I786" s="51" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="787" spans="1:9">
       <c r="A787" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B787" s="5" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C787" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D787" s="6" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="E787" s="14" t="s">
         <v>38</v>
@@ -33362,21 +33359,21 @@
         <v>226.2</v>
       </c>
       <c r="I787" s="51" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="788" spans="1:9">
       <c r="A788" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B788" s="5" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C788" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D788" s="6" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E788" s="14" t="s">
         <v>38</v>
@@ -33391,21 +33388,21 @@
         <v>222.9</v>
       </c>
       <c r="I788" s="51" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="789" spans="1:9">
       <c r="A789" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B789" s="5" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C789" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D789" s="6" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E789" s="14" t="s">
         <v>38</v>
@@ -33420,21 +33417,21 @@
         <v>213</v>
       </c>
       <c r="I789" s="51" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="790" spans="1:9">
       <c r="A790" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B790" s="5" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C790" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D790" s="6" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E790" s="14" t="s">
         <v>38</v>
@@ -33449,21 +33446,21 @@
         <v>216.6</v>
       </c>
       <c r="I790" s="51" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="791" spans="1:9">
       <c r="A791" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B791" s="5" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C791" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D791" s="6" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E791" s="14" t="s">
         <v>38</v>
@@ -33478,21 +33475,21 @@
         <v>450</v>
       </c>
       <c r="I791" s="51" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="792" spans="1:9">
       <c r="A792" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B792" s="5" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C792" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D792" s="6" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E792" s="14" t="s">
         <v>38</v>
@@ -33507,21 +33504,21 @@
         <v>92</v>
       </c>
       <c r="I792" s="51" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="793" spans="1:9">
       <c r="A793" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B793" s="5" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C793" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D793" s="6" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E793" s="14" t="s">
         <v>38</v>
@@ -33536,21 +33533,21 @@
         <v>248.1</v>
       </c>
       <c r="I793" s="51" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="794" spans="1:9">
       <c r="A794" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B794" s="5" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="C794" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D794" s="6" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="E794" s="14" t="s">
         <v>38</v>
@@ -33565,21 +33562,21 @@
         <v>241.2</v>
       </c>
       <c r="I794" s="51" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="795" spans="1:9">
       <c r="A795" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B795" s="5" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="C795" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D795" s="6" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="E795" s="14" t="s">
         <v>38</v>
@@ -33594,21 +33591,21 @@
         <v>222.3</v>
       </c>
       <c r="I795" s="51" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="796" spans="1:9">
       <c r="A796" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B796" s="5" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="C796" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D796" s="6" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="E796" s="14" t="s">
         <v>38</v>
@@ -33623,21 +33620,21 @@
         <v>364.5</v>
       </c>
       <c r="I796" s="51" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="797" spans="1:9">
       <c r="A797" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B797" s="5" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="C797" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D797" s="6" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="E797" s="14" t="s">
         <v>38</v>
@@ -33652,21 +33649,21 @@
         <v>29</v>
       </c>
       <c r="I797" s="51" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="798" spans="1:9">
       <c r="A798" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B798" s="5" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C798" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D798" s="6" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="E798" s="14" t="s">
         <v>38</v>
@@ -33681,21 +33678,21 @@
         <v>29</v>
       </c>
       <c r="I798" s="51" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="799" spans="1:9">
       <c r="A799" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B799" s="5" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="C799" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D799" s="6" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="E799" s="14" t="s">
         <v>38</v>
@@ -33710,21 +33707,21 @@
         <v>29</v>
       </c>
       <c r="I799" s="51" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="800" spans="1:9">
       <c r="A800" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B800" s="5" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="C800" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D800" s="6" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="E800" s="14" t="s">
         <v>38</v>
@@ -33739,21 +33736,21 @@
         <v>29</v>
       </c>
       <c r="I800" s="51" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="801" spans="1:9">
       <c r="A801" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B801" s="5" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="C801" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D801" s="6" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="E801" s="14" t="s">
         <v>38</v>
@@ -33768,21 +33765,21 @@
         <v>270</v>
       </c>
       <c r="I801" s="51" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="802" spans="1:9">
       <c r="A802" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B802" s="5" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="C802" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D802" s="6" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="E802" s="14" t="s">
         <v>38</v>
@@ -33797,7 +33794,7 @@
         <v>240</v>
       </c>
       <c r="I802" s="51" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="803" spans="1:9">
@@ -33816,16 +33813,16 @@
     </row>
     <row r="804" spans="1:9">
       <c r="A804" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B804" s="5" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="C804" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D804" s="6" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="E804" s="14" t="s">
         <v>139</v>
@@ -33840,7 +33837,7 @@
         <v>217.2</v>
       </c>
       <c r="I804" s="51" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="805" spans="1:9">
@@ -33859,16 +33856,16 @@
     </row>
     <row r="806" spans="1:9">
       <c r="A806" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B806" s="5" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="C806" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D806" s="6" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E806" s="14" t="s">
         <v>65</v>
@@ -33883,21 +33880,21 @@
         <v>71.350000000000009</v>
       </c>
       <c r="I806" s="51" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="807" spans="1:9">
       <c r="A807" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B807" s="5" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="C807" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D807" s="6" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="E807" s="14" t="s">
         <v>65</v>
@@ -33912,21 +33909,21 @@
         <v>74.5</v>
       </c>
       <c r="I807" s="51" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="808" spans="1:9">
       <c r="A808" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B808" s="5" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="C808" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D808" s="6" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="E808" s="14" t="s">
         <v>65</v>
@@ -33941,21 +33938,21 @@
         <v>74.350000000000009</v>
       </c>
       <c r="I808" s="51" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="809" spans="1:9">
       <c r="A809" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B809" s="5" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="C809" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D809" s="6" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="E809" s="14" t="s">
         <v>65</v>
@@ -33970,12 +33967,12 @@
         <v>81.2</v>
       </c>
       <c r="I809" s="51" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="810" spans="1:9">
       <c r="A810" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B810" s="5">
         <v>5667</v>
@@ -33984,7 +33981,7 @@
         <v>19</v>
       </c>
       <c r="D810" s="6" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="E810" s="14" t="s">
         <v>65</v>
@@ -33999,21 +33996,21 @@
         <v>109.2</v>
       </c>
       <c r="I810" s="51" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="811" spans="1:9">
       <c r="A811" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B811" s="5" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="C811" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D811" s="6" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="E811" s="14" t="s">
         <v>65</v>
@@ -34028,21 +34025,21 @@
         <v>205</v>
       </c>
       <c r="I811" s="51" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="812" spans="1:9">
       <c r="A812" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B812" s="5" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="C812" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D812" s="6" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E812" s="14" t="s">
         <v>245</v>
@@ -34057,21 +34054,21 @@
         <v>212.3</v>
       </c>
       <c r="I812" s="51" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="813" spans="1:9">
       <c r="A813" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B813" s="5" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="C813" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D813" s="6" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="E813" s="14" t="s">
         <v>245</v>
@@ -34086,21 +34083,21 @@
         <v>298.14999999999998</v>
       </c>
       <c r="I813" s="51" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="814" spans="1:9">
       <c r="A814" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B814" s="5" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="C814" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D814" s="6" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E814" s="14" t="s">
         <v>856</v>
@@ -34115,24 +34112,24 @@
         <v>447</v>
       </c>
       <c r="I814" s="51" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="815" spans="1:9">
       <c r="A815" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B815" s="5" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C815" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D815" s="6" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E815" s="14" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="F815" s="17">
         <v>1</v>
@@ -34144,21 +34141,21 @@
         <v>618.35</v>
       </c>
       <c r="I815" s="51" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="816" spans="1:9">
       <c r="A816" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B816" s="5" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="C816" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D816" s="6" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E816" s="14" t="s">
         <v>978</v>
@@ -34173,24 +34170,24 @@
         <v>1244.1500000000001</v>
       </c>
       <c r="I816" s="51" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="817" spans="1:9">
       <c r="A817" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B817" s="5" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="C817" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D817" s="6" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E817" s="14" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="F817" s="17">
         <v>1</v>
@@ -34202,24 +34199,24 @@
         <v>1555.55</v>
       </c>
       <c r="I817" s="51" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="818" spans="1:9">
       <c r="A818" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B818" s="5" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="C818" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D818" s="6" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E818" s="14" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="F818" s="17">
         <v>1</v>
@@ -34231,24 +34228,24 @@
         <v>2150</v>
       </c>
       <c r="I818" s="51" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="819" spans="1:9">
       <c r="A819" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B819" s="5" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="C819" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D819" s="6" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E819" s="14" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="F819" s="17">
         <v>1</v>
@@ -34260,24 +34257,24 @@
         <v>5350</v>
       </c>
       <c r="I819" s="51" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="820" spans="1:9">
       <c r="A820" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B820" s="5" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="C820" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D820" s="6" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E820" s="14" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="F820" s="17">
         <v>1</v>
@@ -34289,12 +34286,12 @@
         <v>6450</v>
       </c>
       <c r="I820" s="51" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="821" spans="1:9">
       <c r="A821" s="2" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="B821" s="24"/>
       <c r="C821" s="24"/>
@@ -34306,16 +34303,16 @@
     </row>
     <row r="822" spans="1:9">
       <c r="A822" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B822" s="5" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="C822" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D822" s="6" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="E822" s="14" t="s">
         <v>38</v>
@@ -34330,12 +34327,12 @@
         <v>145.19999999999999</v>
       </c>
       <c r="I822" s="51" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="823" spans="1:9">
       <c r="A823" s="2" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="B823" s="24"/>
       <c r="C823" s="24"/>
@@ -34347,16 +34344,16 @@
     </row>
     <row r="824" spans="1:9">
       <c r="A824" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B824" s="5" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="C824" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D824" s="6" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="E824" s="14" t="s">
         <v>38</v>
@@ -34371,21 +34368,21 @@
         <v>150</v>
       </c>
       <c r="I824" s="51" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="825" spans="1:9">
       <c r="A825" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B825" s="5" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="C825" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D825" s="6" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="E825" s="14" t="s">
         <v>38</v>
@@ -34400,21 +34397,21 @@
         <v>68</v>
       </c>
       <c r="I825" s="51" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="826" spans="1:9">
       <c r="A826" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B826" s="5" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="C826" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D826" s="6" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="E826" s="14" t="s">
         <v>38</v>
@@ -34429,21 +34426,21 @@
         <v>105</v>
       </c>
       <c r="I826" s="51" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="827" spans="1:9">
       <c r="A827" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B827" s="5" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="C827" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D827" s="6" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="E827" s="14" t="s">
         <v>38</v>
@@ -34458,21 +34455,21 @@
         <v>#N/A</v>
       </c>
       <c r="I827" s="51" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="828" spans="1:9">
       <c r="A828" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B828" s="5" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="C828" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D828" s="6" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="E828" s="14" t="s">
         <v>38</v>
@@ -34487,21 +34484,21 @@
         <v>135</v>
       </c>
       <c r="I828" s="51" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="829" spans="1:9">
       <c r="A829" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B829" s="5" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="C829" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D829" s="6" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="E829" s="14" t="s">
         <v>38</v>
@@ -34516,21 +34513,21 @@
         <v>325</v>
       </c>
       <c r="I829" s="51" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="830" spans="1:9">
       <c r="A830" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B830" s="5" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="C830" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D830" s="6" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="E830" s="14" t="s">
         <v>65</v>
@@ -34545,21 +34542,21 @@
         <v>#N/A</v>
       </c>
       <c r="I830" s="51" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="831" spans="1:9">
       <c r="A831" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B831" s="5" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="C831" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D831" s="6" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="E831" s="14" t="s">
         <v>38</v>
@@ -34574,21 +34571,21 @@
         <v>192</v>
       </c>
       <c r="I831" s="51" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="832" spans="1:9">
       <c r="A832" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B832" s="5" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="C832" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D832" s="6" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="E832" s="14" t="s">
         <v>38</v>
@@ -34603,21 +34600,21 @@
         <v>#N/A</v>
       </c>
       <c r="I832" s="51" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="833" spans="1:9">
       <c r="A833" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B833" s="5" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="C833" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D833" s="6" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="E833" s="14" t="s">
         <v>38</v>
@@ -34632,21 +34629,21 @@
         <v>60</v>
       </c>
       <c r="I833" s="51" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="834" spans="1:9">
       <c r="A834" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B834" s="5" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="C834" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D834" s="6" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="E834" s="14" t="s">
         <v>38</v>
@@ -34661,21 +34658,21 @@
         <v>65</v>
       </c>
       <c r="I834" s="51" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="835" spans="1:9">
       <c r="A835" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B835" s="5" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="C835" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D835" s="6" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="E835" s="14" t="s">
         <v>38</v>
@@ -34690,21 +34687,21 @@
         <v>68</v>
       </c>
       <c r="I835" s="51" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="836" spans="1:9">
       <c r="A836" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B836" s="5" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="C836" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D836" s="6" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="E836" s="14" t="s">
         <v>38</v>
@@ -34719,21 +34716,21 @@
         <v>85</v>
       </c>
       <c r="I836" s="51" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="837" spans="1:9">
       <c r="A837" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B837" s="5" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="C837" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D837" s="6" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="E837" s="14" t="s">
         <v>38</v>
@@ -34748,21 +34745,21 @@
         <v>#N/A</v>
       </c>
       <c r="I837" s="51" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="838" spans="1:9">
       <c r="A838" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B838" s="5" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="C838" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D838" s="6" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="E838" s="14" t="s">
         <v>38</v>
@@ -34777,21 +34774,21 @@
         <v>85</v>
       </c>
       <c r="I838" s="51" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="839" spans="1:9">
       <c r="A839" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B839" s="5" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="C839" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D839" s="6" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="E839" s="14" t="s">
         <v>38</v>
@@ -34806,21 +34803,21 @@
         <v>85</v>
       </c>
       <c r="I839" s="51" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="840" spans="1:9">
       <c r="A840" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B840" s="5" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="C840" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D840" s="6" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="E840" s="14" t="s">
         <v>38</v>
@@ -34835,21 +34832,21 @@
         <v>95</v>
       </c>
       <c r="I840" s="51" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="841" spans="1:9">
       <c r="A841" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B841" s="5" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="C841" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D841" s="6" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="E841" s="14" t="s">
         <v>38</v>
@@ -34864,21 +34861,21 @@
         <v>150</v>
       </c>
       <c r="I841" s="51" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="842" spans="1:9">
       <c r="A842" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B842" s="5" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="C842" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D842" s="6" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="E842" s="14" t="s">
         <v>38</v>
@@ -34893,7 +34890,7 @@
         <v>250</v>
       </c>
       <c r="I842" s="51" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="843" spans="1:9">
@@ -34912,16 +34909,16 @@
     </row>
     <row r="844" spans="1:9">
       <c r="A844" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B844" s="5" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="C844" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D844" s="6" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="E844" s="14" t="s">
         <v>65</v>
@@ -34936,21 +34933,21 @@
         <v>#N/A</v>
       </c>
       <c r="I844" s="51" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="845" spans="1:9">
       <c r="A845" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B845" s="5" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="C845" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D845" s="6" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="E845" s="14" t="s">
         <v>65</v>
@@ -34965,12 +34962,12 @@
         <v>#N/A</v>
       </c>
       <c r="I845" s="51" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="846" spans="1:9">
       <c r="A846" s="2" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="B846" s="24"/>
       <c r="C846" s="24"/>
@@ -34982,16 +34979,16 @@
     </row>
     <row r="847" spans="1:9">
       <c r="A847" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B847" s="5" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="C847" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D847" s="6" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="E847" s="14" t="s">
         <v>38</v>
@@ -35006,21 +35003,21 @@
         <v>75</v>
       </c>
       <c r="I847" s="51" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="848" spans="1:9">
       <c r="A848" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B848" s="5" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="C848" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D848" s="6" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="E848" s="14" t="s">
         <v>38</v>
@@ -35035,21 +35032,21 @@
         <v>75</v>
       </c>
       <c r="I848" s="51" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="849" spans="1:9">
       <c r="A849" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B849" s="5" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="C849" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D849" s="6" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="E849" s="14" t="s">
         <v>38</v>
@@ -35064,21 +35061,21 @@
         <v>83.4</v>
       </c>
       <c r="I849" s="51" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="850" spans="1:9">
       <c r="A850" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B850" s="5" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="C850" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D850" s="6" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="E850" s="14" t="s">
         <v>38</v>
@@ -35093,21 +35090,21 @@
         <v>135</v>
       </c>
       <c r="I850" s="51" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="851" spans="1:9">
       <c r="A851" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B851" s="5" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="C851" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D851" s="6" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="E851" s="14" t="s">
         <v>38</v>
@@ -35122,21 +35119,21 @@
         <v>101.4</v>
       </c>
       <c r="I851" s="51" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="852" spans="1:9">
       <c r="A852" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B852" s="5" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="C852" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D852" s="6" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="E852" s="14" t="s">
         <v>38</v>
@@ -35151,21 +35148,21 @@
         <v>135</v>
       </c>
       <c r="I852" s="51" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="853" spans="1:9">
       <c r="A853" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B853" s="5" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="C853" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D853" s="6" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="E853" s="14" t="s">
         <v>38</v>
@@ -35180,21 +35177,21 @@
         <v>144</v>
       </c>
       <c r="I853" s="51" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="854" spans="1:9">
       <c r="A854" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B854" s="5" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="C854" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D854" s="6" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="E854" s="14" t="s">
         <v>38</v>
@@ -35209,21 +35206,21 @@
         <v>60</v>
       </c>
       <c r="I854" s="51" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="855" spans="1:9">
       <c r="A855" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B855" s="5" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="C855" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D855" s="6" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="E855" s="14" t="s">
         <v>38</v>
@@ -35238,21 +35235,21 @@
         <v>65</v>
       </c>
       <c r="I855" s="51" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="856" spans="1:9">
       <c r="A856" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B856" s="5" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="C856" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D856" s="6" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="E856" s="14" t="s">
         <v>38</v>
@@ -35267,21 +35264,21 @@
         <v>195</v>
       </c>
       <c r="I856" s="51" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="857" spans="1:9">
       <c r="A857" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B857" s="5" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="C857" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D857" s="6" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="E857" s="14" t="s">
         <v>38</v>
@@ -35296,21 +35293,21 @@
         <v>101.4</v>
       </c>
       <c r="I857" s="51" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="858" spans="1:9">
       <c r="A858" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B858" s="5" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="C858" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D858" s="6" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="E858" s="14" t="s">
         <v>38</v>
@@ -35325,21 +35322,21 @@
         <v>150</v>
       </c>
       <c r="I858" s="51" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="859" spans="1:9">
       <c r="A859" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B859" s="5" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="C859" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D859" s="6" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="E859" s="14" t="s">
         <v>38</v>
@@ -35354,21 +35351,21 @@
         <v>61</v>
       </c>
       <c r="I859" s="51" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="860" spans="1:9">
       <c r="A860" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B860" s="5" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="C860" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D860" s="6" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="E860" s="14" t="s">
         <v>38</v>
@@ -35383,21 +35380,21 @@
         <v>42</v>
       </c>
       <c r="I860" s="51" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="861" spans="1:9">
       <c r="A861" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B861" s="5" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="C861" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D861" s="6" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="E861" s="14" t="s">
         <v>38</v>
@@ -35412,21 +35409,21 @@
         <v>65</v>
       </c>
       <c r="I861" s="51" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="862" spans="1:9">
       <c r="A862" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B862" s="5" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="C862" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D862" s="6" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="E862" s="14" t="s">
         <v>38</v>
@@ -35441,21 +35438,21 @@
         <v>78</v>
       </c>
       <c r="I862" s="51" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="863" spans="1:9">
       <c r="A863" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B863" s="5" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="C863" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D863" s="6" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="E863" s="14" t="s">
         <v>38</v>
@@ -35470,21 +35467,21 @@
         <v>85</v>
       </c>
       <c r="I863" s="51" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="864" spans="1:9">
       <c r="A864" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B864" s="5" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="C864" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D864" s="6" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="E864" s="14" t="s">
         <v>38</v>
@@ -35499,21 +35496,21 @@
         <v>175</v>
       </c>
       <c r="I864" s="51" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="865" spans="1:9">
       <c r="A865" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B865" s="5" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="C865" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D865" s="6" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="E865" s="14" t="s">
         <v>38</v>
@@ -35528,12 +35525,12 @@
         <v>220</v>
       </c>
       <c r="I865" s="51" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="866" spans="1:9">
       <c r="A866" s="2" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="B866" s="24"/>
       <c r="C866" s="24"/>
@@ -35545,16 +35542,16 @@
     </row>
     <row r="867" spans="1:9">
       <c r="A867" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B867" s="5" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="C867" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D867" s="6" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="E867" s="14" t="s">
         <v>38</v>
@@ -35569,21 +35566,21 @@
         <v>41.400000000000013</v>
       </c>
       <c r="I867" s="51" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="868" spans="1:9">
       <c r="A868" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B868" s="5" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="C868" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D868" s="6" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="E868" s="14" t="s">
         <v>38</v>
@@ -35598,12 +35595,12 @@
         <v>67.2</v>
       </c>
       <c r="I868" s="51" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="869" spans="1:9">
       <c r="A869" s="2" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B869" s="24"/>
       <c r="C869" s="24"/>
@@ -35615,16 +35612,16 @@
     </row>
     <row r="870" spans="1:9">
       <c r="A870" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B870" s="5" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="C870" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D870" s="6" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="E870" s="14" t="s">
         <v>38</v>
@@ -35639,21 +35636,21 @@
         <v>70.5</v>
       </c>
       <c r="I870" s="51" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="871" spans="1:9">
       <c r="A871" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B871" s="5" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="C871" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D871" s="6" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="E871" s="14" t="s">
         <v>38</v>
@@ -35668,21 +35665,21 @@
         <v>75.600000000000009</v>
       </c>
       <c r="I871" s="51" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="872" spans="1:9">
       <c r="A872" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B872" s="5" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="C872" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D872" s="6" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="E872" s="14" t="s">
         <v>38</v>
@@ -35697,21 +35694,21 @@
         <v>97.800000000000011</v>
       </c>
       <c r="I872" s="51" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="873" spans="1:9">
       <c r="A873" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B873" s="5" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="C873" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D873" s="6" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="E873" s="14" t="s">
         <v>38</v>
@@ -35726,12 +35723,12 @@
         <v>115.5</v>
       </c>
       <c r="I873" s="51" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="874" spans="1:9">
       <c r="A874" s="2" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="B874" s="24"/>
       <c r="C874" s="24"/>
@@ -35743,16 +35740,16 @@
     </row>
     <row r="875" spans="1:9">
       <c r="A875" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B875" s="5" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="C875" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D875" s="6" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="E875" s="14" t="s">
         <v>38</v>
@@ -35767,21 +35764,21 @@
         <v>97.800000000000011</v>
       </c>
       <c r="I875" s="51" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="876" spans="1:9">
       <c r="A876" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B876" s="5" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="C876" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D876" s="6" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="E876" s="14" t="s">
         <v>38</v>
@@ -35796,21 +35793,21 @@
         <v>125.1</v>
       </c>
       <c r="I876" s="51" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="877" spans="1:9">
       <c r="A877" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B877" s="5" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="C877" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D877" s="6" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="E877" s="14" t="s">
         <v>38</v>
@@ -35825,21 +35822,21 @@
         <v>123.3</v>
       </c>
       <c r="I877" s="51" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="878" spans="1:9">
       <c r="A878" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B878" s="5" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="C878" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D878" s="6" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="E878" s="14" t="s">
         <v>38</v>
@@ -35854,21 +35851,21 @@
         <v>123.3</v>
       </c>
       <c r="I878" s="51" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="879" spans="1:9">
       <c r="A879" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B879" s="5" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="C879" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D879" s="6" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="E879" s="14" t="s">
         <v>38</v>
@@ -35883,21 +35880,21 @@
         <v>109.2</v>
       </c>
       <c r="I879" s="51" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="880" spans="1:9">
       <c r="A880" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B880" s="5" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="C880" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D880" s="6" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="E880" s="14" t="s">
         <v>38</v>
@@ -35912,12 +35909,12 @@
         <v>137.1</v>
       </c>
       <c r="I880" s="51" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="881" spans="1:9">
       <c r="A881" s="2" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="B881" s="24"/>
       <c r="C881" s="24"/>
@@ -35929,16 +35926,16 @@
     </row>
     <row r="882" spans="1:9">
       <c r="A882" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B882" s="5" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="C882" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D882" s="6" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="E882" s="14" t="s">
         <v>38</v>
@@ -35953,21 +35950,21 @@
         <v>120.9</v>
       </c>
       <c r="I882" s="51" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="883" spans="1:9">
       <c r="A883" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B883" s="5" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="C883" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D883" s="6" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="E883" s="14" t="s">
         <v>38</v>
@@ -35982,21 +35979,21 @@
         <v>193.2</v>
       </c>
       <c r="I883" s="51" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="884" spans="1:9">
       <c r="A884" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B884" s="5" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="C884" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D884" s="6" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="E884" s="14" t="s">
         <v>38</v>
@@ -36011,21 +36008,21 @@
         <v>180.9</v>
       </c>
       <c r="I884" s="51" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="885" spans="1:9">
       <c r="A885" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B885" s="5" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="C885" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D885" s="6" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="E885" s="14" t="s">
         <v>38</v>
@@ -36040,21 +36037,21 @@
         <v>100</v>
       </c>
       <c r="I885" s="51" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="886" spans="1:9">
       <c r="A886" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B886" s="5" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="C886" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D886" s="6" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="E886" s="14" t="s">
         <v>38</v>
@@ -36069,21 +36066,21 @@
         <v>95.600000000000009</v>
       </c>
       <c r="I886" s="51" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="887" spans="1:9">
       <c r="A887" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B887" s="5" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="C887" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D887" s="6" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="E887" s="14" t="s">
         <v>38</v>
@@ -36098,21 +36095,21 @@
         <v>109.6</v>
       </c>
       <c r="I887" s="51" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="888" spans="1:9">
       <c r="A888" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B888" s="5" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="C888" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D888" s="6" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="E888" s="14" t="s">
         <v>38</v>
@@ -36127,21 +36124,21 @@
         <v>124.3</v>
       </c>
       <c r="I888" s="51" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="889" spans="1:9">
       <c r="A889" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B889" s="5" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="C889" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D889" s="6" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="E889" s="14" t="s">
         <v>38</v>
@@ -36156,21 +36153,21 @@
         <v>95.600000000000009</v>
       </c>
       <c r="I889" s="51" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="890" spans="1:9">
       <c r="A890" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B890" s="5" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="C890" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D890" s="6" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="E890" s="14" t="s">
         <v>38</v>
@@ -36185,21 +36182,21 @@
         <v>129.85</v>
       </c>
       <c r="I890" s="51" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="891" spans="1:9">
       <c r="A891" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B891" s="5" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="C891" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D891" s="6" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="E891" s="14" t="s">
         <v>38</v>
@@ -36214,21 +36211,21 @@
         <v>125.6</v>
       </c>
       <c r="I891" s="51" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="892" spans="1:9">
       <c r="A892" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B892" s="5" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="C892" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D892" s="6" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="E892" s="14" t="s">
         <v>38</v>
@@ -36243,7 +36240,7 @@
         <v>119.7</v>
       </c>
       <c r="I892" s="51" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="893" spans="1:9">
@@ -36262,16 +36259,16 @@
     </row>
     <row r="894" spans="1:9">
       <c r="A894" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B894" s="5" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="C894" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D894" s="6" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="E894" s="14" t="s">
         <v>65</v>
@@ -36286,21 +36283,21 @@
         <v>330.4</v>
       </c>
       <c r="I894" s="51" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="895" spans="1:9">
       <c r="A895" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B895" s="5" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="C895" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D895" s="6" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="E895" s="14" t="s">
         <v>65</v>
@@ -36315,21 +36312,21 @@
         <v>191.3</v>
       </c>
       <c r="I895" s="51" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="896" spans="1:9">
       <c r="A896" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B896" s="5" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="C896" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D896" s="6" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="E896" s="14" t="s">
         <v>65</v>
@@ -36344,12 +36341,12 @@
         <v>191.3</v>
       </c>
       <c r="I896" s="51" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="897" spans="1:9">
       <c r="A897" s="2" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="B897" s="24"/>
       <c r="C897" s="24"/>
@@ -36361,16 +36358,16 @@
     </row>
     <row r="898" spans="1:9">
       <c r="A898" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B898" s="5" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="C898" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D898" s="6" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="E898" s="14" t="s">
         <v>38</v>
@@ -36385,21 +36382,21 @@
         <v>117.3</v>
       </c>
       <c r="I898" s="51" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="899" spans="1:9">
       <c r="A899" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B899" s="5" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="C899" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D899" s="6" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="E899" s="14" t="s">
         <v>38</v>
@@ -36414,12 +36411,12 @@
         <v>164.1</v>
       </c>
       <c r="I899" s="51" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="900" spans="1:9">
       <c r="A900" s="2" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="B900" s="24"/>
       <c r="C900" s="24"/>
@@ -36431,16 +36428,16 @@
     </row>
     <row r="901" spans="1:9">
       <c r="A901" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B901" s="5" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="C901" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D901" s="6" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="E901" s="14" t="s">
         <v>38</v>
@@ -36455,12 +36452,12 @@
         <v>123.3</v>
       </c>
       <c r="I901" s="51" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="902" spans="1:9">
       <c r="A902" s="2" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="B902" s="24"/>
       <c r="C902" s="24"/>
@@ -36472,16 +36469,16 @@
     </row>
     <row r="903" spans="1:9">
       <c r="A903" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B903" s="5" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="C903" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D903" s="6" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="E903" s="14" t="s">
         <v>38</v>
@@ -36496,12 +36493,12 @@
         <v>68.7</v>
       </c>
       <c r="I903" s="51" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="904" spans="1:9">
       <c r="A904" s="2" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="B904" s="24"/>
       <c r="C904" s="24"/>
@@ -36513,16 +36510,16 @@
     </row>
     <row r="905" spans="1:9">
       <c r="A905" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B905" s="5" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="C905" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D905" s="6" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="E905" s="14" t="s">
         <v>38</v>
@@ -36537,21 +36534,21 @@
         <v>95.7</v>
       </c>
       <c r="I905" s="51" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="906" spans="1:9">
       <c r="A906" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B906" s="5" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="C906" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D906" s="6" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="E906" s="14" t="s">
         <v>38</v>
@@ -36566,21 +36563,21 @@
         <v>182.4</v>
       </c>
       <c r="I906" s="51" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="907" spans="1:9">
       <c r="A907" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B907" s="5" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="C907" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D907" s="6" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="E907" s="14" t="s">
         <v>65</v>
@@ -36595,12 +36592,12 @@
         <v>79.350000000000009</v>
       </c>
       <c r="I907" s="51" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="908" spans="1:9">
       <c r="A908" s="2" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="B908" s="24"/>
       <c r="C908" s="24"/>
@@ -36612,16 +36609,16 @@
     </row>
     <row r="909" spans="1:9">
       <c r="A909" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B909" s="5" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="C909" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D909" s="6" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="E909" s="14" t="s">
         <v>38</v>
@@ -36636,21 +36633,21 @@
         <v>72.3</v>
       </c>
       <c r="I909" s="51" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="910" spans="1:9">
       <c r="A910" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B910" s="5" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="C910" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D910" s="6" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="E910" s="14" t="s">
         <v>38</v>
@@ -36665,21 +36662,21 @@
         <v>72.3</v>
       </c>
       <c r="I910" s="51" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="911" spans="1:9">
       <c r="A911" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B911" s="5" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="C911" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D911" s="6" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="E911" s="14" t="s">
         <v>38</v>
@@ -36694,21 +36691,21 @@
         <v>127.25</v>
       </c>
       <c r="I911" s="51" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="912" spans="1:9">
       <c r="A912" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B912" s="5" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="C912" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D912" s="6" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="E912" s="14" t="s">
         <v>38</v>
@@ -36723,21 +36720,21 @@
         <v>141.75</v>
       </c>
       <c r="I912" s="51" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="913" spans="1:9">
       <c r="A913" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B913" s="5" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="C913" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D913" s="6" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="E913" s="14" t="s">
         <v>38</v>
@@ -36752,12 +36749,12 @@
         <v>150</v>
       </c>
       <c r="I913" s="51" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="914" spans="1:9">
       <c r="A914" s="2" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="B914" s="24"/>
       <c r="C914" s="24"/>
@@ -36769,16 +36766,16 @@
     </row>
     <row r="915" spans="1:9">
       <c r="A915" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B915" s="5" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="C915" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D915" s="6" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="E915" s="14" t="s">
         <v>38</v>
@@ -36793,21 +36790,21 @@
         <v>65.100000000000009</v>
       </c>
       <c r="I915" s="51" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="916" spans="1:9">
       <c r="A916" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B916" s="5" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="C916" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D916" s="6" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="E916" s="14" t="s">
         <v>38</v>
@@ -36822,21 +36819,21 @@
         <v>82.800000000000011</v>
       </c>
       <c r="I916" s="51" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="917" spans="1:9">
       <c r="A917" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B917" s="5" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="C917" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D917" s="6" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="E917" s="14" t="s">
         <v>38</v>
@@ -36851,7 +36848,7 @@
         <v>129</v>
       </c>
       <c r="I917" s="51" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="918" spans="1:9" ht="15.6" customHeight="1">
@@ -36859,7 +36856,7 @@
       <c r="B918" s="45"/>
       <c r="C918" s="46"/>
       <c r="D918" s="47" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="E918" s="46"/>
       <c r="F918" s="46"/>
@@ -36868,7 +36865,7 @@
     </row>
     <row r="919" spans="1:9">
       <c r="A919" s="2" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="B919" s="24"/>
       <c r="C919" s="24"/>
@@ -36880,16 +36877,16 @@
     </row>
     <row r="920" spans="1:9">
       <c r="A920" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B920" s="5" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="C920" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D920" s="6" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="E920" s="14" t="s">
         <v>38</v>
@@ -36904,21 +36901,21 @@
         <v>52.2</v>
       </c>
       <c r="I920" s="51" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="921" spans="1:9">
       <c r="A921" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B921" s="5" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="C921" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D921" s="6" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="E921" s="14" t="s">
         <v>38</v>
@@ -36933,12 +36930,12 @@
         <v>58.2</v>
       </c>
       <c r="I921" s="51" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="922" spans="1:9">
       <c r="A922" s="2" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="B922" s="24"/>
       <c r="C922" s="24"/>
@@ -36950,16 +36947,16 @@
     </row>
     <row r="923" spans="1:9">
       <c r="A923" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B923" s="5" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="C923" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D923" s="6" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="E923" s="14" t="s">
         <v>38</v>
@@ -36974,21 +36971,21 @@
         <v>69</v>
       </c>
       <c r="I923" s="51" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="924" spans="1:9">
       <c r="A924" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B924" s="5" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="C924" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D924" s="6" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="E924" s="14" t="s">
         <v>38</v>
@@ -37003,21 +37000,21 @@
         <v>123</v>
       </c>
       <c r="I924" s="51" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="925" spans="1:9">
       <c r="A925" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B925" s="5" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="C925" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D925" s="6" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="E925" s="14" t="s">
         <v>38</v>
@@ -37032,21 +37029,21 @@
         <v>69</v>
       </c>
       <c r="I925" s="51" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="926" spans="1:9">
       <c r="A926" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B926" s="5" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="C926" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D926" s="6" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="E926" s="14" t="s">
         <v>38</v>
@@ -37061,7 +37058,7 @@
         <v>123</v>
       </c>
       <c r="I926" s="51" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="927" spans="1:9">
@@ -37080,16 +37077,16 @@
     </row>
     <row r="928" spans="1:9">
       <c r="A928" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B928" s="5" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="C928" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D928" s="48" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="E928" s="14" t="s">
         <v>65</v>
@@ -37104,12 +37101,12 @@
         <v>120</v>
       </c>
       <c r="I928" s="51" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="929" spans="1:9">
       <c r="A929" s="2" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="B929" s="24"/>
       <c r="C929" s="24"/>
@@ -37121,16 +37118,16 @@
     </row>
     <row r="930" spans="1:9">
       <c r="A930" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B930" s="5" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="C930" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D930" s="6" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="E930" s="14" t="s">
         <v>38</v>
@@ -37145,21 +37142,21 @@
         <v>83.4</v>
       </c>
       <c r="I930" s="51" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="931" spans="1:9">
       <c r="A931" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B931" s="5" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="C931" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D931" s="6" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="E931" s="14" t="s">
         <v>38</v>
@@ -37174,21 +37171,21 @@
         <v>111</v>
       </c>
       <c r="I931" s="51" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="932" spans="1:9">
       <c r="A932" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B932" s="5" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="C932" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D932" s="6" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="E932" s="14" t="s">
         <v>38</v>
@@ -37203,12 +37200,12 @@
         <v>117.6</v>
       </c>
       <c r="I932" s="51" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="933" spans="1:9">
       <c r="A933" s="2" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="B933" s="24"/>
       <c r="C933" s="24"/>
@@ -37220,16 +37217,16 @@
     </row>
     <row r="934" spans="1:9">
       <c r="A934" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B934" s="5" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="C934" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D934" s="6" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="E934" s="14" t="s">
         <v>38</v>
@@ -37244,21 +37241,21 @@
         <v>141</v>
       </c>
       <c r="I934" s="51" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="935" spans="1:9">
       <c r="A935" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B935" s="5" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="C935" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D935" s="6" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="E935" s="14" t="s">
         <v>38</v>
@@ -37273,21 +37270,21 @@
         <v>74.400000000000006</v>
       </c>
       <c r="I935" s="51" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="936" spans="1:9">
       <c r="A936" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B936" s="5" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="C936" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D936" s="6" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="E936" s="14" t="s">
         <v>38</v>
@@ -37302,21 +37299,21 @@
         <v>141</v>
       </c>
       <c r="I936" s="51" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="937" spans="1:9">
       <c r="A937" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B937" s="5" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="C937" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D937" s="6" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="E937" s="14" t="s">
         <v>38</v>
@@ -37331,21 +37328,21 @@
         <v>74.400000000000006</v>
       </c>
       <c r="I937" s="51" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="938" spans="1:9">
       <c r="A938" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B938" s="5" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="C938" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D938" s="6" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="E938" s="14" t="s">
         <v>38</v>
@@ -37360,21 +37357,21 @@
         <v>88.800000000000011</v>
       </c>
       <c r="I938" s="51" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="939" spans="1:9">
       <c r="A939" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B939" s="5" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="C939" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D939" s="6" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="E939" s="14" t="s">
         <v>38</v>
@@ -37389,21 +37386,21 @@
         <v>180</v>
       </c>
       <c r="I939" s="51" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="940" spans="1:9">
       <c r="A940" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B940" s="5" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="C940" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D940" s="6" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="E940" s="14" t="s">
         <v>38</v>
@@ -37418,21 +37415,21 @@
         <v>141</v>
       </c>
       <c r="I940" s="51" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="941" spans="1:9">
       <c r="A941" s="4" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B941" s="5" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="C941" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D941" s="6" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="E941" s="14" t="s">
         <v>38</v>
@@ -37447,7 +37444,7 @@
         <v>74.400000000000006</v>
       </c>
       <c r="I941" s="51" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="942" spans="1:9" ht="15.6" customHeight="1">
@@ -37455,7 +37452,7 @@
       <c r="B942" s="45"/>
       <c r="C942" s="46"/>
       <c r="D942" s="47" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="E942" s="46"/>
       <c r="F942" s="46"/>
@@ -37464,7 +37461,7 @@
     </row>
     <row r="943" spans="1:9">
       <c r="A943" s="2" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="B943" s="24"/>
       <c r="C943" s="24"/>
@@ -37476,16 +37473,16 @@
     </row>
     <row r="944" spans="1:9">
       <c r="A944" s="4" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B944" s="5" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="C944" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D944" s="6" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="E944" s="14" t="s">
         <v>38</v>
@@ -37500,21 +37497,21 @@
         <v>60</v>
       </c>
       <c r="I944" s="51" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="945" spans="1:9">
       <c r="A945" s="4" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B945" s="5" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="C945" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D945" s="6" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="E945" s="14" t="s">
         <v>38</v>
@@ -37529,21 +37526,21 @@
         <v>126.3</v>
       </c>
       <c r="I945" s="51" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="946" spans="1:9">
       <c r="A946" s="4" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B946" s="5" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="C946" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D946" s="6" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="E946" s="14" t="s">
         <v>38</v>
@@ -37558,21 +37555,21 @@
         <v>96</v>
       </c>
       <c r="I946" s="51" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="947" spans="1:9">
       <c r="A947" s="4" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B947" s="5" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="C947" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D947" s="6" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="E947" s="14" t="s">
         <v>38</v>
@@ -37587,21 +37584,21 @@
         <v>180</v>
       </c>
       <c r="I947" s="51" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="948" spans="1:9">
       <c r="A948" s="4" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B948" s="5" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="C948" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D948" s="6" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="E948" s="14" t="s">
         <v>38</v>
@@ -37616,21 +37613,21 @@
         <v>180</v>
       </c>
       <c r="I948" s="51" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="949" spans="1:9">
       <c r="A949" s="4" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B949" s="5" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="C949" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D949" s="6" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="E949" s="14" t="s">
         <v>38</v>
@@ -37645,21 +37642,21 @@
         <v>72</v>
       </c>
       <c r="I949" s="51" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="950" spans="1:9">
       <c r="A950" s="4" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B950" s="5" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="C950" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D950" s="6" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="E950" s="14" t="s">
         <v>38</v>
@@ -37674,21 +37671,21 @@
         <v>144</v>
       </c>
       <c r="I950" s="51" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="951" spans="1:9">
       <c r="A951" s="4" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B951" s="5" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="C951" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D951" s="6" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="E951" s="14" t="s">
         <v>38</v>
@@ -37703,7 +37700,7 @@
         <v>144</v>
       </c>
       <c r="I951" s="51" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="952" spans="1:9" ht="15.6" customHeight="1">
@@ -37711,7 +37708,7 @@
       <c r="B952" s="45"/>
       <c r="C952" s="46"/>
       <c r="D952" s="47" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="E952" s="46"/>
       <c r="F952" s="46"/>
@@ -37720,7 +37717,7 @@
     </row>
     <row r="953" spans="1:9">
       <c r="A953" s="2" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="B953" s="24"/>
       <c r="C953" s="24"/>
@@ -37732,16 +37729,16 @@
     </row>
     <row r="954" spans="1:9">
       <c r="A954" s="4" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B954" s="5" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="C954" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D954" s="6" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="E954" s="14" t="s">
         <v>38</v>
@@ -37756,21 +37753,21 @@
         <v>65.400000000000006</v>
       </c>
       <c r="I954" s="51" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="955" spans="1:9">
       <c r="A955" s="4" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B955" s="5" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="C955" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D955" s="6" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="E955" s="14" t="s">
         <v>38</v>
@@ -37785,21 +37782,21 @@
         <v>117.6</v>
       </c>
       <c r="I955" s="51" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="956" spans="1:9">
       <c r="A956" s="4" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B956" s="5" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="C956" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D956" s="6" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="E956" s="14" t="s">
         <v>38</v>
@@ -37814,21 +37811,21 @@
         <v>159</v>
       </c>
       <c r="I956" s="51" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="957" spans="1:9">
       <c r="A957" s="4" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B957" s="5" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="C957" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D957" s="6" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="E957" s="14" t="s">
         <v>38</v>
@@ -37843,21 +37840,21 @@
         <v>164.4</v>
       </c>
       <c r="I957" s="51" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="958" spans="1:9">
       <c r="A958" s="4" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B958" s="5" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="C958" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D958" s="6" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="E958" s="14" t="s">
         <v>38</v>
@@ -37872,21 +37869,21 @@
         <v>65.400000000000006</v>
       </c>
       <c r="I958" s="51" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="959" spans="1:9">
       <c r="A959" s="4" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B959" s="5" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="C959" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D959" s="6" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="E959" s="14" t="s">
         <v>38</v>
@@ -37901,21 +37898,21 @@
         <v>125.4</v>
       </c>
       <c r="I959" s="51" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="960" spans="1:9">
       <c r="A960" s="4" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B960" s="5" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="C960" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D960" s="6" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="E960" s="14" t="s">
         <v>38</v>
@@ -37930,21 +37927,21 @@
         <v>159</v>
       </c>
       <c r="I960" s="51" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="961" spans="1:9">
       <c r="A961" s="4" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B961" s="5" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="C961" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D961" s="6" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="E961" s="14" t="s">
         <v>38</v>
@@ -37959,21 +37956,21 @@
         <v>164.4</v>
       </c>
       <c r="I961" s="51" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="962" spans="1:9">
       <c r="A962" s="4" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B962" s="5" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="C962" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D962" s="6" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="E962" s="14" t="s">
         <v>38</v>
@@ -37988,21 +37985,21 @@
         <v>166.5</v>
       </c>
       <c r="I962" s="51" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="963" spans="1:9">
       <c r="A963" s="4" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B963" s="5" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="C963" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D963" s="6" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="E963" s="14" t="s">
         <v>38</v>
@@ -38017,7 +38014,7 @@
         <v>58.5</v>
       </c>
       <c r="I963" s="51" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="964" spans="1:9" ht="15.6" customHeight="1">
@@ -38025,7 +38022,7 @@
       <c r="B964" s="45"/>
       <c r="C964" s="46"/>
       <c r="D964" s="47" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="E964" s="46"/>
       <c r="F964" s="46"/>
@@ -38034,7 +38031,7 @@
     </row>
     <row r="965" spans="1:9">
       <c r="A965" s="24" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="B965" s="24"/>
       <c r="C965" s="24"/>
@@ -38046,16 +38043,16 @@
     </row>
     <row r="966" spans="1:9">
       <c r="A966" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B966" s="5" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="C966" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D966" s="6" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="E966" s="14" t="s">
         <v>38</v>
@@ -38070,21 +38067,21 @@
         <v>144</v>
       </c>
       <c r="I966" s="51" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="967" spans="1:9">
       <c r="A967" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B967" s="5" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="C967" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D967" s="6" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="E967" s="14" t="s">
         <v>38</v>
@@ -38099,21 +38096,21 @@
         <v>71.400000000000006</v>
       </c>
       <c r="I967" s="51" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="968" spans="1:9">
       <c r="A968" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B968" s="5" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="C968" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D968" s="6" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="E968" s="14" t="s">
         <v>38</v>
@@ -38128,21 +38125,21 @@
         <v>94.2</v>
       </c>
       <c r="I968" s="51" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="969" spans="1:9">
       <c r="A969" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B969" s="5" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="C969" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D969" s="6" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="E969" s="14" t="s">
         <v>38</v>
@@ -38157,21 +38154,21 @@
         <v>71.400000000000006</v>
       </c>
       <c r="I969" s="51" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="970" spans="1:9">
       <c r="A970" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B970" s="5" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="C970" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D970" s="6" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="E970" s="14" t="s">
         <v>38</v>
@@ -38186,21 +38183,21 @@
         <v>71.400000000000006</v>
       </c>
       <c r="I970" s="51" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="971" spans="1:9">
       <c r="A971" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B971" s="5" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="C971" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D971" s="6" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="E971" s="14" t="s">
         <v>38</v>
@@ -38215,21 +38212,21 @@
         <v>71.400000000000006</v>
       </c>
       <c r="I971" s="51" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="972" spans="1:9">
       <c r="A972" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B972" s="5" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="C972" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D972" s="6" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="E972" s="14" t="s">
         <v>38</v>
@@ -38244,21 +38241,21 @@
         <v>71.400000000000006</v>
       </c>
       <c r="I972" s="51" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="973" spans="1:9">
       <c r="A973" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B973" s="5" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="C973" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D973" s="6" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="E973" s="14" t="s">
         <v>38</v>
@@ -38273,21 +38270,21 @@
         <v>94.2</v>
       </c>
       <c r="I973" s="51" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="974" spans="1:9">
       <c r="A974" s="4" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B974" s="5" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="C974" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D974" s="6" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="E974" s="14" t="s">
         <v>38</v>
@@ -38302,7 +38299,7 @@
         <v>140.4</v>
       </c>
       <c r="I974" s="51" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="975" spans="1:9" ht="15.6" customHeight="1">
@@ -38310,7 +38307,7 @@
       <c r="B975" s="45"/>
       <c r="C975" s="46"/>
       <c r="D975" s="47" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="E975" s="46"/>
       <c r="F975" s="46"/>
@@ -38319,7 +38316,7 @@
     </row>
     <row r="976" spans="1:9">
       <c r="A976" s="2" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B976" s="24"/>
       <c r="C976" s="24"/>
@@ -38331,16 +38328,16 @@
     </row>
     <row r="977" spans="1:9">
       <c r="A977" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B977" s="5" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="C977" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D977" s="6" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="E977" s="14" t="s">
         <v>38</v>
@@ -38355,21 +38352,21 @@
         <v>45</v>
       </c>
       <c r="I977" s="51" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="978" spans="1:9">
       <c r="A978" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B978" s="5" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="C978" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D978" s="6" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="E978" s="14" t="s">
         <v>38</v>
@@ -38384,21 +38381,21 @@
         <v>45</v>
       </c>
       <c r="I978" s="51" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="979" spans="1:9">
       <c r="A979" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B979" s="5" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="C979" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D979" s="6" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="E979" s="14" t="s">
         <v>38</v>
@@ -38413,21 +38410,21 @@
         <v>228.6</v>
       </c>
       <c r="I979" s="51" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="980" spans="1:9">
       <c r="A980" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B980" s="5" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="C980" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D980" s="6" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="E980" s="14" t="s">
         <v>38</v>
@@ -38442,21 +38439,21 @@
         <v>190.8</v>
       </c>
       <c r="I980" s="51" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="981" spans="1:9">
       <c r="A981" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B981" s="5" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="C981" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D981" s="6" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="E981" s="14" t="s">
         <v>38</v>
@@ -38471,21 +38468,21 @@
         <v>190.8</v>
       </c>
       <c r="I981" s="51" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="982" spans="1:9">
       <c r="A982" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B982" s="5" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C982" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D982" s="6" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="E982" s="14" t="s">
         <v>38</v>
@@ -38500,21 +38497,21 @@
         <v>34.85</v>
       </c>
       <c r="I982" s="51" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="983" spans="1:9">
       <c r="A983" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B983" s="5" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="C983" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D983" s="6" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="E983" s="14" t="s">
         <v>38</v>
@@ -38529,21 +38526,21 @@
         <v>32.25</v>
       </c>
       <c r="I983" s="51" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="984" spans="1:9">
       <c r="A984" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B984" s="5" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="C984" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D984" s="6" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="E984" s="14" t="s">
         <v>38</v>
@@ -38558,21 +38555,21 @@
         <v>226.8</v>
       </c>
       <c r="I984" s="51" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="985" spans="1:9">
       <c r="A985" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B985" s="5" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="C985" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D985" s="6" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="E985" s="14" t="s">
         <v>38</v>
@@ -38587,21 +38584,21 @@
         <v>49.3</v>
       </c>
       <c r="I985" s="51" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="986" spans="1:9">
       <c r="A986" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B986" s="5" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="C986" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D986" s="6" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="E986" s="14" t="s">
         <v>38</v>
@@ -38616,12 +38613,12 @@
         <v>65.350000000000009</v>
       </c>
       <c r="I986" s="51" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="987" spans="1:9">
       <c r="A987" s="2" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="B987" s="24"/>
       <c r="C987" s="24"/>
@@ -38633,16 +38630,16 @@
     </row>
     <row r="988" spans="1:9">
       <c r="A988" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B988" s="5" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="C988" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D988" s="6" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="E988" s="14" t="s">
         <v>38</v>
@@ -38657,21 +38654,21 @@
         <v>69.7</v>
       </c>
       <c r="I988" s="51" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="989" spans="1:9">
       <c r="A989" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B989" s="5" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="C989" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D989" s="6" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="E989" s="14" t="s">
         <v>38</v>
@@ -38686,7 +38683,7 @@
         <v>151</v>
       </c>
       <c r="I989" s="51" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="990" spans="1:9">
@@ -38705,16 +38702,16 @@
     </row>
     <row r="991" spans="1:9">
       <c r="A991" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B991" s="5" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C991" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D991" s="6" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="E991" s="14" t="s">
         <v>65</v>
@@ -38729,12 +38726,12 @@
         <v>294.05</v>
       </c>
       <c r="I991" s="51" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="992" spans="1:9">
       <c r="A992" s="2" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="B992" s="24"/>
       <c r="C992" s="24"/>
@@ -38746,16 +38743,16 @@
     </row>
     <row r="993" spans="1:9">
       <c r="A993" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B993" s="5" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C993" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D993" s="6" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="E993" s="14" t="s">
         <v>38</v>
@@ -38770,21 +38767,21 @@
         <v>72</v>
       </c>
       <c r="I993" s="51" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="994" spans="1:9">
       <c r="A994" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B994" s="5" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C994" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D994" s="6" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="E994" s="14" t="s">
         <v>38</v>
@@ -38799,7 +38796,7 @@
         <v>125</v>
       </c>
       <c r="I994" s="51" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="995" spans="1:9">
@@ -38818,16 +38815,16 @@
     </row>
     <row r="996" spans="1:9">
       <c r="A996" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B996" s="5" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C996" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D996" s="6" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="E996" s="14" t="s">
         <v>65</v>
@@ -38842,21 +38839,21 @@
         <v>145</v>
       </c>
       <c r="I996" s="51" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="997" spans="1:9">
       <c r="A997" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B997" s="5" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="C997" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D997" s="6" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="E997" s="14" t="s">
         <v>65</v>
@@ -38871,12 +38868,12 @@
         <v>265</v>
       </c>
       <c r="I997" s="51" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="998" spans="1:9">
       <c r="A998" s="2" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="B998" s="24"/>
       <c r="C998" s="24"/>
@@ -38888,16 +38885,16 @@
     </row>
     <row r="999" spans="1:9">
       <c r="A999" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B999" s="5" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="C999" s="53" t="s">
         <v>10</v>
       </c>
       <c r="D999" s="6" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="E999" s="14" t="s">
         <v>38</v>
@@ -38912,21 +38909,21 @@
         <v>110</v>
       </c>
       <c r="I999" s="51" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="1000" spans="1:9">
       <c r="A1000" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B1000" s="5" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
       <c r="C1000" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1000" s="6" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="E1000" s="14" t="s">
         <v>38</v>
@@ -38941,21 +38938,21 @@
         <v>200</v>
       </c>
       <c r="I1000" s="51" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="1001" spans="1:9">
       <c r="A1001" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B1001" s="5" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="C1001" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1001" s="6" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="E1001" s="14" t="s">
         <v>38</v>
@@ -38970,21 +38967,21 @@
         <v>450</v>
       </c>
       <c r="I1001" s="51" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="1002" spans="1:9">
       <c r="A1002" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B1002" s="5" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="C1002" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1002" s="6" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="E1002" s="14" t="s">
         <v>38</v>
@@ -38999,12 +38996,12 @@
         <v>450</v>
       </c>
       <c r="I1002" s="51" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="1003" spans="1:9">
       <c r="A1003" s="2" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="B1003" s="24"/>
       <c r="C1003" s="24"/>
@@ -39016,16 +39013,16 @@
     </row>
     <row r="1004" spans="1:9">
       <c r="A1004" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B1004" s="5" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="C1004" s="53" t="s">
         <v>10</v>
       </c>
       <c r="D1004" s="6" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="E1004" s="14" t="s">
         <v>38</v>
@@ -39040,21 +39037,21 @@
         <v>95</v>
       </c>
       <c r="I1004" s="51" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="1005" spans="1:9">
       <c r="A1005" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B1005" s="5" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="C1005" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1005" s="6" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="E1005" s="14" t="s">
         <v>38</v>
@@ -39069,7 +39066,7 @@
         <v>90</v>
       </c>
       <c r="I1005" s="51" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="1006" spans="1:9" ht="15.6" customHeight="1">
@@ -39077,7 +39074,7 @@
       <c r="B1006" s="45"/>
       <c r="C1006" s="46"/>
       <c r="D1006" s="47" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="E1006" s="46"/>
       <c r="F1006" s="46"/>
@@ -39086,7 +39083,7 @@
     </row>
     <row r="1007" spans="1:9">
       <c r="A1007" s="2" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="B1007" s="24"/>
       <c r="C1007" s="24"/>
@@ -39098,16 +39095,16 @@
     </row>
     <row r="1008" spans="1:9">
       <c r="A1008" s="4" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="B1008" s="5" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="C1008" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1008" s="6" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="E1008" s="14" t="s">
         <v>38</v>
@@ -39122,21 +39119,21 @@
         <v>53.400000000000013</v>
       </c>
       <c r="I1008" s="51" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="1009" spans="1:9">
       <c r="A1009" s="4" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="B1009" s="5" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="C1009" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1009" s="6" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="E1009" s="14" t="s">
         <v>38</v>
@@ -39151,21 +39148,21 @@
         <v>53.400000000000013</v>
       </c>
       <c r="I1009" s="51" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="1010" spans="1:9">
       <c r="A1010" s="4" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="B1010" s="5" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="C1010" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1010" s="6" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="E1010" s="14" t="s">
         <v>38</v>
@@ -39180,21 +39177,21 @@
         <v>75</v>
       </c>
       <c r="I1010" s="51" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="1011" spans="1:9">
       <c r="A1011" s="4" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="B1011" s="5" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="C1011" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1011" s="6" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="E1011" s="14" t="s">
         <v>38</v>
@@ -39209,21 +39206,21 @@
         <v>150</v>
       </c>
       <c r="I1011" s="51" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="1012" spans="1:9">
       <c r="A1012" s="4" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="B1012" s="5" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="C1012" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1012" s="6" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="E1012" s="14" t="s">
         <v>38</v>
@@ -39238,7 +39235,7 @@
         <v>135</v>
       </c>
       <c r="I1012" s="51" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="1013" spans="1:9" ht="15.6" customHeight="1">
@@ -39246,7 +39243,7 @@
       <c r="B1013" s="45"/>
       <c r="C1013" s="46"/>
       <c r="D1013" s="47" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="E1013" s="46"/>
       <c r="F1013" s="46"/>
@@ -39255,7 +39252,7 @@
     </row>
     <row r="1014" spans="1:9">
       <c r="A1014" s="2" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="B1014" s="24"/>
       <c r="C1014" s="24"/>
@@ -39267,16 +39264,16 @@
     </row>
     <row r="1015" spans="1:9">
       <c r="A1015" s="4" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B1015" s="5" t="s">
         <v>2598</v>
-      </c>
-      <c r="B1015" s="5" t="s">
-        <v>2599</v>
       </c>
       <c r="C1015" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1015" s="6" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="E1015" s="14" t="s">
         <v>38</v>
@@ -39291,21 +39288,21 @@
         <v>51.599999999999987</v>
       </c>
       <c r="I1015" s="51" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="1016" spans="1:9">
       <c r="A1016" s="4" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="B1016" s="5" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="C1016" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1016" s="6" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="E1016" s="14" t="s">
         <v>38</v>
@@ -39320,21 +39317,21 @@
         <v>48.599999999999987</v>
       </c>
       <c r="I1016" s="51" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="1017" spans="1:9">
       <c r="A1017" s="4" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="B1017" s="5" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="C1017" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1017" s="6" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="E1017" s="14" t="s">
         <v>38</v>
@@ -39349,7 +39346,7 @@
         <v>48.599999999999987</v>
       </c>
       <c r="I1017" s="51" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="1018" spans="1:9" ht="15.6" customHeight="1">
@@ -39357,7 +39354,7 @@
       <c r="B1018" s="45"/>
       <c r="C1018" s="46"/>
       <c r="D1018" s="47" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="E1018" s="46"/>
       <c r="F1018" s="46"/>
@@ -39366,7 +39363,7 @@
     </row>
     <row r="1019" spans="1:9">
       <c r="A1019" s="2" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="B1019" s="24"/>
       <c r="C1019" s="24"/>
@@ -39381,13 +39378,13 @@
         <v>789</v>
       </c>
       <c r="B1020" s="4" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="C1020" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1020" s="4" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="E1020" s="14" t="s">
         <v>38</v>
@@ -39402,7 +39399,7 @@
         <v>45.6</v>
       </c>
       <c r="I1020" s="51" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="1021" spans="1:9">
@@ -39410,13 +39407,13 @@
         <v>789</v>
       </c>
       <c r="B1021" s="4" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="C1021" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1021" s="4" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="E1021" s="14" t="s">
         <v>38</v>
@@ -39431,7 +39428,7 @@
         <v>45.6</v>
       </c>
       <c r="I1021" s="51" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="1022" spans="1:9">
@@ -39439,13 +39436,13 @@
         <v>789</v>
       </c>
       <c r="B1022" s="4" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="C1022" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1022" s="4" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="E1022" s="14" t="s">
         <v>38</v>
@@ -39460,7 +39457,7 @@
         <v>79.800000000000011</v>
       </c>
       <c r="I1022" s="51" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="1023" spans="1:9">
@@ -39468,13 +39465,13 @@
         <v>789</v>
       </c>
       <c r="B1023" s="4" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="C1023" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1023" s="4" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="E1023" s="14" t="s">
         <v>38</v>
@@ -39489,12 +39486,12 @@
         <v>93</v>
       </c>
       <c r="I1023" s="51" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="1024" spans="1:9">
       <c r="A1024" s="2" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="B1024" s="2"/>
       <c r="C1024" s="2"/>
@@ -39509,13 +39506,13 @@
         <v>789</v>
       </c>
       <c r="B1025" s="5" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="C1025" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1025" s="6" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="E1025" s="14" t="s">
         <v>38</v>
@@ -39530,7 +39527,7 @@
         <v>78.600000000000009</v>
       </c>
       <c r="I1025" s="51" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="1026" spans="1:9">
@@ -39538,13 +39535,13 @@
         <v>789</v>
       </c>
       <c r="B1026" s="5" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="C1026" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1026" s="6" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="E1026" s="14" t="s">
         <v>38</v>
@@ -39559,12 +39556,12 @@
         <v>42</v>
       </c>
       <c r="I1026" s="51" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="1027" spans="1:9">
       <c r="A1027" s="2" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="B1027" s="2"/>
       <c r="C1027" s="2"/>
@@ -39579,13 +39576,13 @@
         <v>789</v>
       </c>
       <c r="B1028" s="5" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="C1028" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1028" s="6" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="E1028" s="14" t="s">
         <v>38</v>
@@ -39600,7 +39597,7 @@
         <v>55.8</v>
       </c>
       <c r="I1028" s="51" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="1029" spans="1:9">
@@ -39608,13 +39605,13 @@
         <v>789</v>
       </c>
       <c r="B1029" s="5" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="C1029" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1029" s="6" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="E1029" s="14" t="s">
         <v>38</v>
@@ -39629,7 +39626,7 @@
         <v>84.600000000000009</v>
       </c>
       <c r="I1029" s="51" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="1030" spans="1:9">
@@ -39637,13 +39634,13 @@
         <v>789</v>
       </c>
       <c r="B1030" s="5" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="C1030" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1030" s="6" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="E1030" s="14" t="s">
         <v>38</v>
@@ -39658,12 +39655,12 @@
         <v>49.2</v>
       </c>
       <c r="I1030" s="51" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="1031" spans="1:9">
       <c r="A1031" s="2" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="B1031" s="2"/>
       <c r="C1031" s="2"/>
@@ -39676,13 +39673,13 @@
     <row r="1032" spans="1:9">
       <c r="A1032" s="4"/>
       <c r="B1032" s="4" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="C1032" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1032" s="4" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="E1032" s="14" t="s">
         <v>38</v>
@@ -39697,12 +39694,12 @@
         <v>49.2</v>
       </c>
       <c r="I1032" s="51" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="1033" spans="1:9">
       <c r="A1033" s="2" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="B1033" s="2"/>
       <c r="C1033" s="2"/>
@@ -39717,13 +39714,13 @@
         <v>789</v>
       </c>
       <c r="B1034" s="5" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="C1034" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1034" s="6" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="E1034" s="14" t="s">
         <v>38</v>
@@ -39738,12 +39735,12 @@
         <v>58.8</v>
       </c>
       <c r="I1034" s="51" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="1035" spans="1:9">
       <c r="A1035" s="2" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="B1035" s="2"/>
       <c r="C1035" s="2"/>
@@ -39758,13 +39755,13 @@
         <v>1095</v>
       </c>
       <c r="B1036" s="5" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="C1036" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1036" s="6" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="E1036" s="14" t="s">
         <v>38</v>
@@ -39779,7 +39776,7 @@
         <v>43.8</v>
       </c>
       <c r="I1036" s="51" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="1037" spans="1:9">
@@ -39787,13 +39784,13 @@
         <v>1095</v>
       </c>
       <c r="B1037" s="5" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="C1037" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1037" s="6" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="E1037" s="14" t="s">
         <v>65</v>
@@ -39808,7 +39805,7 @@
         <v>12.6</v>
       </c>
       <c r="I1037" s="51" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="1038" spans="1:9">
@@ -39816,13 +39813,13 @@
         <v>1095</v>
       </c>
       <c r="B1038" s="5" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="C1038" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1038" s="6" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="E1038" s="14" t="s">
         <v>38</v>
@@ -39837,7 +39834,7 @@
         <v>43.8</v>
       </c>
       <c r="I1038" s="51" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="1039" spans="1:9">
@@ -39857,13 +39854,13 @@
         <v>396</v>
       </c>
       <c r="B1040" s="5" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="C1040" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1040" s="6" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="E1040" s="14" t="s">
         <v>38</v>
@@ -39878,7 +39875,7 @@
         <v>57</v>
       </c>
       <c r="I1040" s="51" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="1041" spans="1:9">
@@ -39886,13 +39883,13 @@
         <v>396</v>
       </c>
       <c r="B1041" s="5" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="C1041" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1041" s="28" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="E1041" s="14" t="s">
         <v>38</v>
@@ -39907,7 +39904,7 @@
         <v>63</v>
       </c>
       <c r="I1041" s="51" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="1042" spans="1:9">
@@ -39915,13 +39912,13 @@
         <v>396</v>
       </c>
       <c r="B1042" s="5" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="C1042" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1042" s="6" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="E1042" s="14" t="s">
         <v>38</v>
@@ -39936,7 +39933,7 @@
         <v>47.400000000000013</v>
       </c>
       <c r="I1042" s="51" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="1043" spans="1:9">
@@ -39944,13 +39941,13 @@
         <v>396</v>
       </c>
       <c r="B1043" s="5" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="C1043" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1043" s="6" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="E1043" s="14" t="s">
         <v>38</v>
@@ -39965,7 +39962,7 @@
         <v>64.2</v>
       </c>
       <c r="I1043" s="51" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="1044" spans="1:9">
@@ -39973,13 +39970,13 @@
         <v>396</v>
       </c>
       <c r="B1044" s="5" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="C1044" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1044" s="6" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="E1044" s="14" t="s">
         <v>65</v>
@@ -39994,7 +39991,7 @@
         <v>37.799999999999997</v>
       </c>
       <c r="I1044" s="51" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="1045" spans="1:9">
@@ -40002,13 +39999,13 @@
         <v>396</v>
       </c>
       <c r="B1045" s="5" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="C1045" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1045" s="6" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="E1045" s="14" t="s">
         <v>65</v>
@@ -40023,12 +40020,12 @@
         <v>39.6</v>
       </c>
       <c r="I1045" s="51" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="1046" spans="1:9">
       <c r="A1046" s="2" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="B1046" s="24"/>
       <c r="C1046" s="24"/>
@@ -40041,13 +40038,13 @@
     <row r="1047" spans="1:9">
       <c r="A1047" s="4"/>
       <c r="B1047" s="5" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="C1047" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1047" s="6" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="E1047" s="14" t="s">
         <v>38</v>
@@ -40062,19 +40059,19 @@
         <v>42</v>
       </c>
       <c r="I1047" s="51" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="1048" spans="1:9">
       <c r="A1048" s="4"/>
       <c r="B1048" s="5" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="C1048" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1048" s="6" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="E1048" s="14" t="s">
         <v>38</v>
@@ -40089,19 +40086,19 @@
         <v>46.8</v>
       </c>
       <c r="I1048" s="51" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="1049" spans="1:9">
       <c r="A1049" s="4"/>
       <c r="B1049" s="5" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="C1049" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1049" s="6" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="E1049" s="14" t="s">
         <v>38</v>
@@ -40116,19 +40113,19 @@
         <v>46.8</v>
       </c>
       <c r="I1049" s="51" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="1050" spans="1:9">
       <c r="A1050" s="4"/>
       <c r="B1050" s="5" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="C1050" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1050" s="6" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="E1050" s="14" t="s">
         <v>38</v>
@@ -40143,19 +40140,19 @@
         <v>46.8</v>
       </c>
       <c r="I1050" s="51" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="1051" spans="1:9">
       <c r="A1051" s="4"/>
       <c r="B1051" s="5" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="C1051" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1051" s="6" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="E1051" s="14" t="s">
         <v>38</v>
@@ -40170,19 +40167,19 @@
         <v>46.8</v>
       </c>
       <c r="I1051" s="51" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="1052" spans="1:9">
       <c r="A1052" s="4"/>
       <c r="B1052" s="5" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="C1052" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1052" s="6" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="E1052" s="14" t="s">
         <v>38</v>
@@ -40197,19 +40194,19 @@
         <v>46.8</v>
       </c>
       <c r="I1052" s="51" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="1053" spans="1:9">
       <c r="A1053" s="4"/>
       <c r="B1053" s="5" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="C1053" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1053" s="6" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="E1053" s="14" t="s">
         <v>38</v>
@@ -40224,19 +40221,19 @@
         <v>42</v>
       </c>
       <c r="I1053" s="51" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="1054" spans="1:9">
       <c r="A1054" s="4"/>
       <c r="B1054" s="5" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="C1054" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1054" s="6" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="E1054" s="14" t="s">
         <v>38</v>
@@ -40251,19 +40248,19 @@
         <v>44.400000000000013</v>
       </c>
       <c r="I1054" s="51" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="1055" spans="1:9">
       <c r="A1055" s="4"/>
       <c r="B1055" s="5" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="C1055" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1055" s="6" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="E1055" s="14" t="s">
         <v>38</v>
@@ -40278,19 +40275,19 @@
         <v>44.400000000000013</v>
       </c>
       <c r="I1055" s="51" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="1056" spans="1:9">
       <c r="A1056" s="4"/>
       <c r="B1056" s="5" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="C1056" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1056" s="6" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="E1056" s="14" t="s">
         <v>38</v>
@@ -40305,12 +40302,12 @@
         <v>46.8</v>
       </c>
       <c r="I1056" s="51" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="1057" spans="1:9">
       <c r="A1057" s="2" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="B1057" s="24"/>
       <c r="C1057" s="24"/>
@@ -40323,13 +40320,13 @@
     <row r="1058" spans="1:9">
       <c r="A1058" s="4"/>
       <c r="B1058" s="5" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="C1058" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1058" s="6" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
       <c r="E1058" s="14" t="s">
         <v>38</v>
@@ -40344,19 +40341,19 @@
         <v>41.400000000000013</v>
       </c>
       <c r="I1058" s="51" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="1059" spans="1:9">
       <c r="A1059" s="4"/>
       <c r="B1059" s="5" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="C1059" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1059" s="6" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
       <c r="E1059" s="14" t="s">
         <v>38</v>
@@ -40371,12 +40368,12 @@
         <v>41.400000000000013</v>
       </c>
       <c r="I1059" s="51" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="1060" spans="1:9">
       <c r="A1060" s="2" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="B1060" s="24"/>
       <c r="C1060" s="24"/>
@@ -40391,13 +40388,13 @@
         <v>35</v>
       </c>
       <c r="B1061" s="4" t="s">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="C1061" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1061" s="4" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
       <c r="E1061" s="14" t="s">
         <v>38</v>
@@ -40412,7 +40409,7 @@
         <v>73.2</v>
       </c>
       <c r="I1061" s="51" t="s">
-        <v>2714</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="1062" spans="1:9">
@@ -40420,13 +40417,13 @@
         <v>35</v>
       </c>
       <c r="B1062" s="4" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="C1062" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1062" s="4" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="E1062" s="14" t="s">
         <v>38</v>
@@ -40441,7 +40438,7 @@
         <v>65.400000000000006</v>
       </c>
       <c r="I1062" s="51" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="1063" spans="1:9">
@@ -40449,13 +40446,13 @@
         <v>35</v>
       </c>
       <c r="B1063" s="4" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
       <c r="C1063" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1063" s="4" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="E1063" s="14" t="s">
         <v>65</v>
@@ -40470,7 +40467,7 @@
         <v>39</v>
       </c>
       <c r="I1063" s="51" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="1064" spans="1:9">
@@ -40478,13 +40475,13 @@
         <v>35</v>
       </c>
       <c r="B1064" s="4" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="C1064" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1064" s="4" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="E1064" s="14" t="s">
         <v>38</v>
@@ -40499,7 +40496,7 @@
         <v>65.400000000000006</v>
       </c>
       <c r="I1064" s="51" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="1065" spans="1:9">
@@ -40507,13 +40504,13 @@
         <v>35</v>
       </c>
       <c r="B1065" s="4" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="C1065" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1065" s="4" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="E1065" s="14" t="s">
         <v>65</v>
@@ -40528,7 +40525,7 @@
         <v>42.3</v>
       </c>
       <c r="I1065" s="51" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="1066" spans="1:9">
@@ -40536,13 +40533,13 @@
         <v>35</v>
       </c>
       <c r="B1066" s="4" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C1066" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1066" s="4" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
       <c r="E1066" s="14" t="s">
         <v>38</v>
@@ -40557,7 +40554,7 @@
         <v>83.7</v>
       </c>
       <c r="I1066" s="51" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="1067" spans="1:9" ht="15.6" customHeight="1">
@@ -40565,7 +40562,7 @@
       <c r="B1067" s="45"/>
       <c r="C1067" s="46"/>
       <c r="D1067" s="47" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="E1067" s="46"/>
       <c r="F1067" s="46"/>
@@ -40574,7 +40571,7 @@
     </row>
     <row r="1068" spans="1:9">
       <c r="A1068" s="2" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="B1068" s="24"/>
       <c r="C1068" s="24"/>
@@ -40595,7 +40592,7 @@
         <v>19</v>
       </c>
       <c r="D1069" s="6" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="E1069" s="14" t="s">
         <v>38</v>
@@ -40610,7 +40607,7 @@
         <v>102</v>
       </c>
       <c r="I1069" s="51" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1070" spans="1:9">
@@ -40618,13 +40615,13 @@
         <v>396</v>
       </c>
       <c r="B1070" s="5" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="C1070" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1070" s="6" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="E1070" s="14" t="s">
         <v>38</v>
@@ -40639,7 +40636,7 @@
         <v>102</v>
       </c>
       <c r="I1070" s="51" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="1071" spans="1:9">
@@ -40647,13 +40644,13 @@
         <v>396</v>
       </c>
       <c r="B1071" s="5" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
       <c r="C1071" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1071" s="6" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="E1071" s="14" t="s">
         <v>38</v>
@@ -40668,7 +40665,7 @@
         <v>131.4</v>
       </c>
       <c r="I1071" s="51" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="1072" spans="1:9">
@@ -40676,13 +40673,13 @@
         <v>396</v>
       </c>
       <c r="B1072" s="5" t="s">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="C1072" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1072" s="6" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
       <c r="E1072" s="14" t="s">
         <v>38</v>
@@ -40697,7 +40694,7 @@
         <v>131.4</v>
       </c>
       <c r="I1072" s="51" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="1073" spans="1:9">
@@ -40705,13 +40702,13 @@
         <v>396</v>
       </c>
       <c r="B1073" s="30" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C1073" s="55" t="s">
         <v>50</v>
       </c>
       <c r="D1073" s="31" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="E1073" s="32" t="s">
         <v>38</v>
@@ -40726,7 +40723,7 @@
         <v>129</v>
       </c>
       <c r="I1073" s="51" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="1074" spans="1:9">
@@ -40748,13 +40745,13 @@
         <v>396</v>
       </c>
       <c r="B1075" s="5" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="C1075" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1075" s="6" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="E1075" s="14" t="s">
         <v>65</v>
@@ -40769,12 +40766,12 @@
         <v>33.450000000000003</v>
       </c>
       <c r="I1075" s="51" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="1076" spans="1:9">
       <c r="A1076" s="2" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="B1076" s="2"/>
       <c r="C1076" s="2"/>
@@ -40789,13 +40786,13 @@
         <v>396</v>
       </c>
       <c r="B1077" s="5" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="C1077" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1077" s="6" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
       <c r="E1077" s="14" t="s">
         <v>38</v>
@@ -40810,12 +40807,12 @@
         <v>164.7</v>
       </c>
       <c r="I1077" s="51" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="1078" spans="1:9">
       <c r="A1078" s="2" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="B1078" s="2"/>
       <c r="C1078" s="2"/>
@@ -40830,13 +40827,13 @@
         <v>396</v>
       </c>
       <c r="B1079" s="8" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="C1079" s="53" t="s">
         <v>19</v>
       </c>
       <c r="D1079" s="9" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="E1079" s="15" t="s">
         <v>38</v>
@@ -40851,7 +40848,7 @@
         <v>108.3</v>
       </c>
       <c r="I1079" s="51" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="1080" spans="1:9">
@@ -40859,13 +40856,13 @@
         <v>396</v>
       </c>
       <c r="B1080" s="8" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="C1080" s="53" t="s">
         <v>19</v>
       </c>
       <c r="D1080" s="9" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="E1080" s="15" t="s">
         <v>38</v>
@@ -40880,12 +40877,12 @@
         <v>139.5</v>
       </c>
       <c r="I1080" s="51" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="1081" spans="1:9">
       <c r="A1081" s="2" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="B1081" s="2"/>
       <c r="C1081" s="2"/>
@@ -40900,13 +40897,13 @@
         <v>396</v>
       </c>
       <c r="B1082" s="5" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="C1082" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1082" s="6" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="E1082" s="14" t="s">
         <v>38</v>
@@ -40921,7 +40918,7 @@
         <v>97.800000000000011</v>
       </c>
       <c r="I1082" s="51" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="1083" spans="1:9">
@@ -40935,7 +40932,7 @@
         <v>19</v>
       </c>
       <c r="D1083" s="6" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="E1083" s="14" t="s">
         <v>38</v>
@@ -40950,7 +40947,7 @@
         <v>97.800000000000011</v>
       </c>
       <c r="I1083" s="51" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="1084" spans="1:9">
@@ -40958,13 +40955,13 @@
         <v>396</v>
       </c>
       <c r="B1084" s="5" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="C1084" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1084" s="6" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="E1084" s="14" t="s">
         <v>38</v>
@@ -40979,7 +40976,7 @@
         <v>117.3</v>
       </c>
       <c r="I1084" s="51" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="1085" spans="1:9">
@@ -40993,7 +40990,7 @@
         <v>50</v>
       </c>
       <c r="D1085" s="6" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="E1085" s="14" t="s">
         <v>38</v>
@@ -41008,12 +41005,12 @@
         <v>117.3</v>
       </c>
       <c r="I1085" s="51" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="1086" spans="1:9">
       <c r="A1086" s="2" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="B1086" s="2"/>
       <c r="C1086" s="2"/>
@@ -41028,13 +41025,13 @@
         <v>396</v>
       </c>
       <c r="B1087" s="5" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="C1087" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D1087" s="6" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="E1087" s="14" t="s">
         <v>38</v>
@@ -41049,7 +41046,7 @@
         <v>48.900000000000013</v>
       </c>
       <c r="I1087" s="51" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="1088" spans="1:9">
@@ -41057,13 +41054,13 @@
         <v>396</v>
       </c>
       <c r="B1088" s="5" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="C1088" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1088" s="6" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="E1088" s="14" t="s">
         <v>38</v>
@@ -41078,7 +41075,7 @@
         <v>48.900000000000013</v>
       </c>
       <c r="I1088" s="51" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="1089" spans="1:9">
@@ -41086,13 +41083,13 @@
         <v>396</v>
       </c>
       <c r="B1089" s="5" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="C1089" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1089" s="6" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="E1089" s="14" t="s">
         <v>38</v>
@@ -41107,12 +41104,12 @@
         <v>86.100000000000009</v>
       </c>
       <c r="I1089" s="51" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="1090" spans="1:9">
       <c r="A1090" s="2" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="B1090" s="2"/>
       <c r="C1090" s="2"/>
@@ -41127,13 +41124,13 @@
         <v>396</v>
       </c>
       <c r="B1091" s="5" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="C1091" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1091" s="6" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="E1091" s="14" t="s">
         <v>38</v>
@@ -41148,7 +41145,7 @@
         <v>62.100000000000009</v>
       </c>
       <c r="I1091" s="51" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="1092" spans="1:9">
@@ -41156,13 +41153,13 @@
         <v>396</v>
       </c>
       <c r="B1092" s="5" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="C1092" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1092" s="6" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="E1092" s="14" t="s">
         <v>38</v>
@@ -41177,7 +41174,7 @@
         <v>85.5</v>
       </c>
       <c r="I1092" s="51" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="1093" spans="1:9">
@@ -41191,7 +41188,7 @@
         <v>24</v>
       </c>
       <c r="D1093" s="6" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="E1093" s="14" t="s">
         <v>38</v>
@@ -41206,7 +41203,7 @@
         <v>88.800000000000011</v>
       </c>
       <c r="I1093" s="51" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="1094" spans="1:9">
@@ -41214,13 +41211,13 @@
         <v>396</v>
       </c>
       <c r="B1094" s="5" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="C1094" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1094" s="6" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="E1094" s="14" t="s">
         <v>38</v>
@@ -41235,7 +41232,7 @@
         <v>101.7</v>
       </c>
       <c r="I1094" s="51" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="1095" spans="1:9">
@@ -41243,13 +41240,13 @@
         <v>396</v>
       </c>
       <c r="B1095" s="5" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="C1095" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1095" s="6" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="E1095" s="14" t="s">
         <v>38</v>
@@ -41264,7 +41261,7 @@
         <v>107.1</v>
       </c>
       <c r="I1095" s="51" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="1096" spans="1:9">
@@ -41272,13 +41269,13 @@
         <v>396</v>
       </c>
       <c r="B1096" s="5" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
       <c r="C1096" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1096" s="6" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
       <c r="E1096" s="14" t="s">
         <v>38</v>
@@ -41293,7 +41290,7 @@
         <v>107.7</v>
       </c>
       <c r="I1096" s="51" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="1097" spans="1:9">
@@ -41301,13 +41298,13 @@
         <v>396</v>
       </c>
       <c r="B1097" s="5" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="C1097" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1097" s="6" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
       <c r="E1097" s="14" t="s">
         <v>38</v>
@@ -41322,7 +41319,7 @@
         <v>110.1</v>
       </c>
       <c r="I1097" s="51" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="1098" spans="1:9">
@@ -41330,13 +41327,13 @@
         <v>396</v>
       </c>
       <c r="B1098" s="5" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="C1098" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1098" s="6" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="E1098" s="14" t="s">
         <v>38</v>
@@ -41351,7 +41348,7 @@
         <v>37.049999999999997</v>
       </c>
       <c r="I1098" s="51" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="1099" spans="1:9">
@@ -41359,13 +41356,13 @@
         <v>396</v>
       </c>
       <c r="B1099" s="5" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="C1099" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1099" s="6" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="E1099" s="14" t="s">
         <v>38</v>
@@ -41380,7 +41377,7 @@
         <v>73.600000000000009</v>
       </c>
       <c r="I1099" s="51" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="1100" spans="1:9">
@@ -41399,7 +41396,7 @@
     </row>
     <row r="1101" spans="1:9">
       <c r="A1101" s="2" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="B1101" s="24"/>
       <c r="C1101" s="24"/>
@@ -41411,7 +41408,7 @@
     </row>
     <row r="1102" spans="1:9">
       <c r="A1102" s="7" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="B1102" s="8"/>
       <c r="C1102" s="53" t="s">
@@ -41425,7 +41422,7 @@
     </row>
     <row r="1103" spans="1:9">
       <c r="A1103" s="2" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="B1103" s="2"/>
       <c r="C1103" s="2"/>
@@ -41440,13 +41437,13 @@
         <v>544</v>
       </c>
       <c r="B1104" s="5" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="C1104" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D1104" s="6" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="E1104" s="14" t="s">
         <v>38</v>
@@ -41461,7 +41458,7 @@
         <v>215.1</v>
       </c>
       <c r="I1104" s="51" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="1105" spans="1:9">
@@ -41469,13 +41466,13 @@
         <v>544</v>
       </c>
       <c r="B1105" s="5" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="C1105" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D1105" s="6" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="E1105" s="14" t="s">
         <v>38</v>
@@ -41490,12 +41487,12 @@
         <v>140.1</v>
       </c>
       <c r="I1105" s="51" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="1106" spans="1:9">
       <c r="A1106" s="2" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="B1106" s="2"/>
       <c r="C1106" s="2"/>
@@ -41510,13 +41507,13 @@
         <v>35</v>
       </c>
       <c r="B1107" s="5" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="C1107" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D1107" s="6" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
       <c r="E1107" s="14" t="s">
         <v>38</v>
@@ -41531,7 +41528,7 @@
         <v>34.5</v>
       </c>
       <c r="I1107" s="51" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="1108" spans="1:9">
@@ -41539,13 +41536,13 @@
         <v>35</v>
       </c>
       <c r="B1108" s="5" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="C1108" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D1108" s="6" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="E1108" s="14" t="s">
         <v>38</v>
@@ -41560,7 +41557,7 @@
         <v>26.1</v>
       </c>
       <c r="I1108" s="51" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="1109" spans="1:9">
@@ -41568,13 +41565,13 @@
         <v>35</v>
       </c>
       <c r="B1109" s="5" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="C1109" s="52" t="s">
         <v>272</v>
       </c>
       <c r="D1109" s="6" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="E1109" s="14" t="s">
         <v>38</v>
@@ -41589,12 +41586,12 @@
         <v>28.8</v>
       </c>
       <c r="I1109" s="51" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="1110" spans="1:9">
       <c r="A1110" s="2" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="B1110" s="2"/>
       <c r="C1110" s="2"/>
@@ -41609,13 +41606,13 @@
         <v>1095</v>
       </c>
       <c r="B1111" s="5" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="C1111" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1111" s="6" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="E1111" s="14" t="s">
         <v>38</v>
@@ -41630,7 +41627,7 @@
         <v>24</v>
       </c>
       <c r="I1111" s="51" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="1112" spans="1:9">
@@ -41638,13 +41635,13 @@
         <v>1095</v>
       </c>
       <c r="B1112" s="5" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="C1112" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1112" s="6" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="E1112" s="14" t="s">
         <v>38</v>
@@ -41659,7 +41656,7 @@
         <v>24</v>
       </c>
       <c r="I1112" s="51" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="1113" spans="1:9">
@@ -41667,13 +41664,13 @@
         <v>1095</v>
       </c>
       <c r="B1113" s="5" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="C1113" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1113" s="6" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c r="E1113" s="14" t="s">
         <v>38</v>
@@ -41688,7 +41685,7 @@
         <v>26.7</v>
       </c>
       <c r="I1113" s="51" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="1114" spans="1:9">
@@ -41696,13 +41693,13 @@
         <v>1095</v>
       </c>
       <c r="B1114" s="5" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="C1114" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1114" s="6" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="E1114" s="14" t="s">
         <v>65</v>
@@ -41717,7 +41714,7 @@
         <v>41.400000000000013</v>
       </c>
       <c r="I1114" s="51" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="1115" spans="1:9">
@@ -41725,13 +41722,13 @@
         <v>1095</v>
       </c>
       <c r="B1115" s="5" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="C1115" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1115" s="6" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="E1115" s="14" t="s">
         <v>38</v>
@@ -41746,7 +41743,7 @@
         <v>44.1</v>
       </c>
       <c r="I1115" s="51" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="1116" spans="1:9">
@@ -41754,13 +41751,13 @@
         <v>1095</v>
       </c>
       <c r="B1116" s="5" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="C1116" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1116" s="6" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="E1116" s="14" t="s">
         <v>38</v>
@@ -41775,7 +41772,7 @@
         <v>42.3</v>
       </c>
       <c r="I1116" s="51" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="1117" spans="1:9">
@@ -41783,13 +41780,13 @@
         <v>1095</v>
       </c>
       <c r="B1117" s="5" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="C1117" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1117" s="6" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="E1117" s="14" t="s">
         <v>38</v>
@@ -41804,7 +41801,7 @@
         <v>35.400000000000013</v>
       </c>
       <c r="I1117" s="51" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="1118" spans="1:9">
@@ -41812,13 +41809,13 @@
         <v>1095</v>
       </c>
       <c r="B1118" s="5" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="C1118" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1118" s="6" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="E1118" s="14" t="s">
         <v>38</v>
@@ -41833,7 +41830,7 @@
         <v>31.2</v>
       </c>
       <c r="I1118" s="51" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="1119" spans="1:9">
@@ -41841,13 +41838,13 @@
         <v>1095</v>
       </c>
       <c r="B1119" s="5" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="C1119" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1119" s="6" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="E1119" s="14" t="s">
         <v>38</v>
@@ -41862,7 +41859,7 @@
         <v>35.400000000000013</v>
       </c>
       <c r="I1119" s="51" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="1120" spans="1:9">
@@ -41870,13 +41867,13 @@
         <v>1095</v>
       </c>
       <c r="B1120" s="5" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="C1120" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1120" s="6" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="E1120" s="14" t="s">
         <v>38</v>
@@ -41891,7 +41888,7 @@
         <v>42.900000000000013</v>
       </c>
       <c r="I1120" s="51" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="1121" spans="1:9">
@@ -41899,13 +41896,13 @@
         <v>1095</v>
       </c>
       <c r="B1121" s="5" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="C1121" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1121" s="6" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="E1121" s="14" t="s">
         <v>38</v>
@@ -41920,7 +41917,7 @@
         <v>51.900000000000013</v>
       </c>
       <c r="I1121" s="51" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="1122" spans="1:9">
@@ -41928,13 +41925,13 @@
         <v>1095</v>
       </c>
       <c r="B1122" s="5" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="C1122" s="52" t="s">
         <v>24</v>
       </c>
       <c r="D1122" s="6" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="E1122" s="14" t="s">
         <v>65</v>
@@ -41949,7 +41946,7 @@
         <v>13.25</v>
       </c>
       <c r="I1122" s="51" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="1123" spans="1:9" ht="15.6" customHeight="1">
@@ -41957,7 +41954,7 @@
       <c r="B1123" s="45"/>
       <c r="C1123" s="46"/>
       <c r="D1123" s="47" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="E1123" s="46"/>
       <c r="F1123" s="46"/>
@@ -41966,7 +41963,7 @@
     </row>
     <row r="1124" spans="1:9">
       <c r="A1124" s="2" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="B1124" s="2"/>
       <c r="C1124" s="2"/>
@@ -41978,16 +41975,16 @@
     </row>
     <row r="1125" spans="1:9">
       <c r="A1125" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1125" s="5" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="C1125" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1125" s="6" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="E1125" s="14" t="s">
         <v>38</v>
@@ -42002,21 +41999,21 @@
         <v>297.60000000000002</v>
       </c>
       <c r="I1125" s="51" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="1126" spans="1:9">
       <c r="A1126" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1126" s="5" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="C1126" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1126" s="6" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="E1126" s="14" t="s">
         <v>38</v>
@@ -42031,21 +42028,21 @@
         <v>324</v>
       </c>
       <c r="I1126" s="51" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="1127" spans="1:9">
       <c r="A1127" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1127" s="5" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="C1127" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1127" s="6" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="E1127" s="14" t="s">
         <v>38</v>
@@ -42060,21 +42057,21 @@
         <v>348.9</v>
       </c>
       <c r="I1127" s="51" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="1128" spans="1:9">
       <c r="A1128" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1128" s="5" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="C1128" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1128" s="6" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="E1128" s="14" t="s">
         <v>38</v>
@@ -42089,21 +42086,21 @@
         <v>465.30000000000013</v>
       </c>
       <c r="I1128" s="51" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="1129" spans="1:9">
       <c r="A1129" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1129" s="5" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="C1129" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1129" s="6" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="E1129" s="14" t="s">
         <v>38</v>
@@ -42118,21 +42115,21 @@
         <v>1301.0999999999999</v>
       </c>
       <c r="I1129" s="51" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="1130" spans="1:9">
       <c r="A1130" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1130" s="5" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="C1130" s="52" t="s">
         <v>50</v>
       </c>
       <c r="D1130" s="6" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="E1130" s="14" t="s">
         <v>38</v>
@@ -42147,12 +42144,12 @@
         <v>437.25</v>
       </c>
       <c r="I1130" s="51" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="1131" spans="1:9">
       <c r="A1131" s="7" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="B1131" s="8"/>
       <c r="C1131" s="53" t="s">
@@ -42166,16 +42163,16 @@
     </row>
     <row r="1132" spans="1:9">
       <c r="A1132" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1132" s="5" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="C1132" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1132" s="6" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="E1132" s="14" t="s">
         <v>65</v>
@@ -42190,21 +42187,21 @@
         <v>118.8</v>
       </c>
       <c r="I1132" s="51" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="1133" spans="1:9">
       <c r="A1133" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1133" s="5" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="C1133" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1133" s="6" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="E1133" s="14" t="s">
         <v>65</v>
@@ -42219,12 +42216,12 @@
         <v>120.8</v>
       </c>
       <c r="I1133" s="51" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="1134" spans="1:9">
       <c r="A1134" s="2" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="B1134" s="2"/>
       <c r="C1134" s="2"/>
@@ -42236,16 +42233,16 @@
     </row>
     <row r="1135" spans="1:9">
       <c r="A1135" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1135" s="5" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="C1135" s="52" t="s">
         <v>19</v>
       </c>
       <c r="D1135" s="6" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="E1135" s="14" t="s">
         <v>38</v>
@@ -42260,7 +42257,7 @@
         <v>300</v>
       </c>
       <c r="I1135" s="51" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
     </row>
   </sheetData>
